--- a/OUT_25-26_M2_BM_universites.xlsx
+++ b/OUT_25-26_M2_BM_universites.xlsx
@@ -8,35 +8,47 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coulono\Downloads\Navigo - perso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{5CDEAE52-377D-4B32-99A5-336F5718A700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D41000B-46F1-4427-811F-07176CAB8709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13785" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13785" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Synthèse" sheetId="1" r:id="rId1"/>
-    <sheet name="Universités" sheetId="2" r:id="rId2"/>
-    <sheet name="Afrique" sheetId="3" r:id="rId3"/>
-    <sheet name="Amériques" sheetId="4" r:id="rId4"/>
-    <sheet name="Asie" sheetId="5" r:id="rId5"/>
-    <sheet name="Moyen-Orient" sheetId="6" r:id="rId6"/>
-    <sheet name="Europe" sheetId="7" r:id="rId7"/>
+    <sheet name="Synthèse" sheetId="8" r:id="rId1"/>
+    <sheet name="Tierlist" sheetId="1" r:id="rId2"/>
+    <sheet name="Universités" sheetId="2" r:id="rId3"/>
+    <sheet name="Afrique" sheetId="3" r:id="rId4"/>
+    <sheet name="Amériques" sheetId="4" r:id="rId5"/>
+    <sheet name="Asie" sheetId="5" r:id="rId6"/>
+    <sheet name="Moyen-Orient" sheetId="6" r:id="rId7"/>
+    <sheet name="Europe" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Afrique!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Amériques!$A$1:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Asie!$A$1:$F$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Europe!$A$1:$F$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Moyen-Orient'!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Synthèse!$A$1:$D$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Universités!$A$1:$F$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Afrique!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Amériques!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Asie!$A$1:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Europe!$A$1:$F$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Moyen-Orient'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Universités!$A$1:$F$124</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="366">
   <si>
     <t>Continent</t>
   </si>
@@ -44,9 +56,6 @@
     <t>Pays / région</t>
   </si>
   <si>
-    <t>Nombre d'universités</t>
-  </si>
-  <si>
     <t>Nombre de places</t>
   </si>
   <si>
@@ -170,9 +179,6 @@
     <t>Uk</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Université</t>
   </si>
   <si>
@@ -575,9 +581,6 @@
     <t>🥇 Tier 1 — Incontournables, impact CV maximal</t>
   </si>
   <si>
-    <t>CopyDownload</t>
-  </si>
-  <si>
     <t>#</t>
   </si>
   <si>
@@ -1019,49 +1022,130 @@
     <t>🆕 Profil ingé/tech, bon pour finance quantitative en Asie du Sud-Est</t>
   </si>
   <si>
-    <t>💡 Synthèse stratégique</t>
-  </si>
-  <si>
-    <t>Objectif</t>
-  </si>
-  <si>
-    <t>Top choix dans cette liste</t>
-  </si>
-  <si>
-    <t>Imperial, MIT Sloan, Politecnico Milano, TUM, RWTH Aachen</t>
-  </si>
-  <si>
-    <t>Imperial, Aston, Newcastle</t>
-  </si>
-  <si>
-    <t>Bocconi, Mannheim, Frankfurt School, HEC Lausanne, St. Gallen</t>
-  </si>
-  <si>
-    <t>Fudan, CUHK, Waseda, Keio</t>
-  </si>
-  <si>
-    <t>MIT Sloan, Rice, UNC Chapel Hill</t>
-  </si>
-  <si>
-    <t>HEC Montréal, UBC Sauder, Laval (DD)</t>
-  </si>
-  <si>
-    <t>📐 Quant / Financial Engineering</t>
-  </si>
-  <si>
-    <t>🏦 Trading / Dérivés — London</t>
-  </si>
-  <si>
-    <t>🇪🇺 Finance continentale (Paris, Frankfurt)</t>
-  </si>
-  <si>
-    <t>🌏 Finance en Asie</t>
-  </si>
-  <si>
-    <t>🇺🇸 Wall Street / Buy-side US</t>
-  </si>
-  <si>
-    <t>🇨🇦 Finance — Canada</t>
+    <t>Commentaire</t>
+  </si>
+  <si>
+    <t>non car notes</t>
+  </si>
+  <si>
+    <t>cher</t>
+  </si>
+  <si>
+    <t>master de con en sustainability</t>
+  </si>
+  <si>
+    <t>allemand LV2 obligatoire</t>
+  </si>
+  <si>
+    <t>Maitreclasse</t>
+  </si>
+  <si>
+    <t>pas les notes</t>
+  </si>
+  <si>
+    <t>?rien pigé aux programmes, pas trouvé sur le site edhec</t>
+  </si>
+  <si>
+    <t>pas trouvé la liste de cours encore…</t>
+  </si>
+  <si>
+    <t>niet : suisse</t>
+  </si>
+  <si>
+    <t>suisse</t>
+  </si>
+  <si>
+    <t>echange existe plus</t>
+  </si>
+  <si>
+    <t>semble plutôt banger ça, beaucoup de cours quantitatifs, visiblement pas de limite sur ce qu'on peut prendre</t>
+  </si>
+  <si>
+    <t>échange cool, cours absolument réduits a néant a cause edhec</t>
+  </si>
+  <si>
+    <t>2 cours intéressants, le reste pue</t>
+  </si>
+  <si>
+    <t>cours vraiment bien (à la fois quantitatif, mais aussi bcp de data), à voir acceptation edhec ("it is not possible to specialize in Economics during this exchange and Finance courses are generally not accepted for credit transfer except courses related to the fields of Accounting and Auditing")</t>
+  </si>
+  <si>
+    <t>cours sustainability de merde</t>
+  </si>
+  <si>
+    <t>choix de cours plutôt large et bien adapté, top cours : Asset management, Money, banking &amp; financial markets, time series analysis &amp; machine learning</t>
+  </si>
+  <si>
+    <t>vraiment bon choix, cours pertinents : Derivatives, neural networks for Eco and Finance, advanced monetary policy, macroeconometrics, time series analysis,asset pricing, financial econometrics</t>
+  </si>
+  <si>
+    <t>programmes pas trop clairs car sont présentés en 2ans, mais programme Msc economic and finance - Advanced eco and finance plutôt pas mal au global</t>
+  </si>
+  <si>
+    <t>idem, cours interessants mais pascompris ce qu'on avait le droit de prendre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big, cours vraiment pertinents, à voir éligibilité edhec </t>
+  </si>
+  <si>
+    <t>Cours vraiment bien sur campus bruxelles (est ce que je veux aller dans cacaville Bruxelles : non)</t>
+  </si>
+  <si>
+    <t>juste pour la chine</t>
+  </si>
+  <si>
+    <t>pas de derivatives, pas d'asset pricing, mais cours quantitatifs quand même</t>
+  </si>
+  <si>
+    <t>pas trouvé la liste de cours</t>
+  </si>
+  <si>
+    <t>que du supply chain ou mgmt</t>
+  </si>
+  <si>
+    <t>rien pané au choix des cours, mais y a des très bons cours quantitatifs</t>
+  </si>
+  <si>
+    <t>gett</t>
+  </si>
+  <si>
+    <t>pas les notes, mais je le met pour expérience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc in Information Science and Technology Management why not, sinon pas ed choses pour front </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chine, sinon pas de bon programme </t>
+  </si>
+  <si>
+    <t>absolu mid pour front, angleterre pourquoi pas</t>
+  </si>
+  <si>
+    <t>GMAT score of 550, ielts6,5, programmes pourraves (ptete information systems and business analytics)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">derivatives dispo : maitreclassique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">idem que WHU koblenz : mid mais reste ok </t>
+  </si>
+  <si>
+    <t>pas trouvé les cours ???</t>
+  </si>
+  <si>
+    <t>site de con, y a rien derriere l'onglet "courses"</t>
+  </si>
+  <si>
+    <t>ptdr erreur 404 sur la liste des cours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pourquoi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2 </t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1201,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1134,11 +1218,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1172,6 +1308,34 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1474,1455 +1638,1295 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J84"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8D01D8-A348-4A3C-A33B-1505E738259C}">
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="1" max="1" width="39.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="141.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:2" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A2,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>Maitreclasse</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A3,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>semble plutôt banger ça, beaucoup de cours quantitatifs, visiblement pas de limite sur ce qu'on peut prendre</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A4,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>cours vraiment bien (à la fois quantitatif, mais aussi bcp de data), à voir acceptation edhec ("it is not possible to specialize in Economics during this exchange and Finance courses are generally not accepted for credit transfer except courses related to the fields of Accounting and Auditing")</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A5,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>choix de cours plutôt large et bien adapté, top cours : Asset management, Money, banking &amp; financial markets, time series analysis &amp; machine learning</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A6,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>vraiment bon choix, cours pertinents : Derivatives, neural networks for Eco and Finance, advanced monetary policy, macroeconometrics, time series analysis,asset pricing, financial econometrics</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="B7" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A7,Tierlist!C:C,Tierlist!A:A)</f>
+        <v xml:space="preserve">Big, cours vraiment pertinents, à voir éligibilité edhec </v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A8,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>Cours vraiment bien sur campus bruxelles (est ce que je veux aller dans cacaville Bruxelles : non)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A9,Tierlist!C:C,Tierlist!A:A)</f>
+        <v xml:space="preserve">derivatives dispo : maitreclassique </v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A10,Tierlist!C:C,Tierlist!A:A)</f>
+        <v xml:space="preserve">idem que WHU koblenz : mid mais reste ok </v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="B11" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A11,Tierlist!C:C,Tierlist!A:A)</f>
+        <v xml:space="preserve">chine, sinon pas de bon programme </v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="20"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="27" t="s">
+        <v>365</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B14" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A14,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>échange cool, cours absolument réduits a néant a cause edhec</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A15,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>2 cours intéressants, le reste pue</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A16,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>programmes pas trop clairs car sont présentés en 2ans, mais programme Msc economic and finance - Advanced eco and finance plutôt pas mal au global</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="B17" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A17,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>idem, cours interessants mais pascompris ce qu'on avait le droit de prendre</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="B18" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A18,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>pas de derivatives, pas d'asset pricing, mais cours quantitatifs quand même</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="B19" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A19,Tierlist!C:C,Tierlist!A:A)</f>
+        <v>rien pané au choix des cours, mais y a des très bons cours quantitatifs</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="B20" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A20,Tierlist!C:C,Tierlist!A:A)</f>
+        <v xml:space="preserve">MSc in Information Science and Technology Management why not, sinon pas ed choses pour front </v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21" s="29" t="str">
+        <f>_xlfn.XLOOKUP(A21,Tierlist!C:C,Tierlist!A:A)</f>
+        <v xml:space="preserve">chine, sinon pas de bon programme </v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E84"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="74.7265625" customWidth="1"/>
+    <col min="2" max="2" width="6.36328125" customWidth="1"/>
+    <col min="3" max="3" width="55.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="81.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C5" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C6" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="B7">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="C7" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="D7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="B8">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C8" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="B9">
         <v>5</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>2</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C9" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="20"/>
+    </row>
+    <row r="11" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="20"/>
+      <c r="B11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="20"/>
+    </row>
+    <row r="13" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="20"/>
+      <c r="B13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="E13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="B14">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C14" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B15">
         <v>7</v>
       </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2">
-        <v>6</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="C15" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="D16" t="s">
+        <v>200</v>
+      </c>
+      <c r="E16" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" t="s">
+        <v>203</v>
+      </c>
+      <c r="E17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" t="s">
+        <v>203</v>
+      </c>
+      <c r="E18" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="B19">
+        <v>11</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="D19" t="s">
+        <v>203</v>
+      </c>
+      <c r="E19" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="B20">
+        <v>12</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="D20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="B21">
+        <v>13</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D21" t="s">
+        <v>190</v>
+      </c>
+      <c r="E21" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="B22">
+        <v>14</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="D22" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D23" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="B24">
+        <v>16</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D24" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="20"/>
+    </row>
+    <row r="26" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="20"/>
+      <c r="B26" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="20"/>
+    </row>
+    <row r="28" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="20"/>
+      <c r="B28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E28" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2">
+    <row r="29" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="B29">
+        <v>17</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D29" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="B30">
+        <v>18</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D30" t="s">
+        <v>190</v>
+      </c>
+      <c r="E30" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="B31">
         <v>19</v>
       </c>
-      <c r="G4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="C31" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D31" t="s">
+        <v>190</v>
+      </c>
+      <c r="E31" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="B32">
+        <v>20</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="D32" t="s">
+        <v>229</v>
+      </c>
+      <c r="E32" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="B33">
+        <v>21</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E33" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="B34">
+        <v>22</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="D34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="B35">
+        <v>23</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D35" t="s">
+        <v>236</v>
+      </c>
+      <c r="E35" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="20"/>
+      <c r="B36">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>238</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E36" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="20"/>
+      <c r="B37">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E37" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="20"/>
+      <c r="B38">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>242</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="E38" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="20"/>
+      <c r="B39">
+        <v>27</v>
+      </c>
+      <c r="C39" t="s">
+        <v>245</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="20"/>
+      <c r="B40">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>247</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="E40" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="20"/>
+      <c r="B41">
+        <v>29</v>
+      </c>
+      <c r="C41" t="s">
+        <v>250</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="E41" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="B42">
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
+        <v>252</v>
+      </c>
+      <c r="D42" t="s">
+        <v>253</v>
+      </c>
+      <c r="E42" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="B43">
+        <v>31</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="D43" t="s">
+        <v>256</v>
+      </c>
+      <c r="E43" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="B44">
+        <v>32</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D44" t="s">
+        <v>256</v>
+      </c>
+      <c r="E44" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="B45">
+        <v>33</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="D45" t="s">
+        <v>261</v>
+      </c>
+      <c r="E45" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="B46">
+        <v>34</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="D46" t="s">
+        <v>261</v>
+      </c>
+      <c r="E46" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="20"/>
+    </row>
+    <row r="48" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="20"/>
+      <c r="B48" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="20"/>
+    </row>
+    <row r="50" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="20"/>
+      <c r="B50" t="s">
+        <v>177</v>
+      </c>
+      <c r="C50" t="s">
+        <v>43</v>
+      </c>
+      <c r="D50" t="s">
+        <v>178</v>
+      </c>
+      <c r="E50" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B51">
+        <v>35</v>
+      </c>
+      <c r="C51" t="s">
+        <v>266</v>
+      </c>
+      <c r="D51" t="s">
+        <v>267</v>
+      </c>
+      <c r="E51" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B52">
+        <v>36</v>
+      </c>
+      <c r="C52" t="s">
+        <v>269</v>
+      </c>
+      <c r="D52" t="s">
+        <v>267</v>
+      </c>
+      <c r="E52" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B53">
+        <v>37</v>
+      </c>
+      <c r="C53" t="s">
+        <v>271</v>
+      </c>
+      <c r="D53" t="s">
+        <v>267</v>
+      </c>
+      <c r="E53" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B54">
+        <v>38</v>
+      </c>
+      <c r="C54" t="s">
+        <v>273</v>
+      </c>
+      <c r="D54" t="s">
+        <v>274</v>
+      </c>
+      <c r="E54" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="B55">
+        <v>39</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="D55" t="s">
+        <v>274</v>
+      </c>
+      <c r="E55" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="B56">
+        <v>40</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="D56" t="s">
+        <v>279</v>
+      </c>
+      <c r="E56" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="B57">
+        <v>41</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="D57" t="s">
+        <v>253</v>
+      </c>
+      <c r="E57" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="B58">
+        <v>42</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="D58" t="s">
+        <v>181</v>
+      </c>
+      <c r="E58" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="B59">
+        <v>43</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="D59" t="s">
+        <v>181</v>
+      </c>
+      <c r="E59" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="B60">
+        <v>44</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="D60" t="s">
+        <v>288</v>
+      </c>
+      <c r="E60" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="B61">
         <v>45</v>
       </c>
-      <c r="I4" t="s">
-        <v>181</v>
-      </c>
-      <c r="J4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>183</v>
-      </c>
-      <c r="I5" t="s">
-        <v>184</v>
-      </c>
-      <c r="J5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6" t="s">
-        <v>186</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="C61" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D61" t="s">
+        <v>291</v>
+      </c>
+      <c r="E61" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="B62">
+        <v>46</v>
+      </c>
+      <c r="C62" t="s">
+        <v>293</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="E62" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="20"/>
+      <c r="B63">
+        <v>47</v>
+      </c>
+      <c r="C63" t="s">
+        <v>295</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="E63" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="20"/>
+      <c r="B64">
+        <v>48</v>
+      </c>
+      <c r="C64" t="s">
+        <v>298</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="E64" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="20"/>
+      <c r="B65">
+        <v>49</v>
+      </c>
+      <c r="C65" t="s">
+        <v>300</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="E65" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="20"/>
+      <c r="B66">
+        <v>50</v>
+      </c>
+      <c r="C66" t="s">
+        <v>302</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="E66" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="20"/>
+      <c r="B67">
+        <v>51</v>
+      </c>
+      <c r="C67" t="s">
+        <v>304</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="E67" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="B68">
+        <v>52</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="D68" t="s">
+        <v>307</v>
+      </c>
+      <c r="E68" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="B69">
+        <v>53</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="D69" t="s">
+        <v>310</v>
+      </c>
+      <c r="E69" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="20"/>
+      <c r="B70">
+        <v>54</v>
+      </c>
+      <c r="C70" t="s">
+        <v>312</v>
+      </c>
+      <c r="D70" t="s">
         <v>187</v>
       </c>
-      <c r="J6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>8</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7" t="s">
-        <v>189</v>
-      </c>
-      <c r="I7" t="s">
-        <v>190</v>
-      </c>
-      <c r="J7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8" t="s">
-        <v>192</v>
-      </c>
-      <c r="I8" t="s">
-        <v>193</v>
-      </c>
-      <c r="J8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2">
-        <v>3</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9" t="s">
-        <v>195</v>
-      </c>
-      <c r="I9" t="s">
-        <v>193</v>
-      </c>
-      <c r="J9" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2">
-        <v>3</v>
-      </c>
-      <c r="G11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="2">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2">
-        <v>37</v>
-      </c>
-      <c r="G12" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="2">
-        <v>4</v>
-      </c>
-      <c r="D13" s="2">
-        <v>9</v>
-      </c>
-      <c r="G13" t="s">
-        <v>180</v>
-      </c>
-      <c r="H13" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" t="s">
-        <v>181</v>
-      </c>
-      <c r="J13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="2">
-        <v>5</v>
-      </c>
-      <c r="D14" s="2">
-        <v>7</v>
-      </c>
-      <c r="G14">
-        <v>6</v>
-      </c>
-      <c r="H14" t="s">
-        <v>198</v>
-      </c>
-      <c r="I14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J14" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>7</v>
-      </c>
-      <c r="H15" t="s">
-        <v>200</v>
-      </c>
-      <c r="I15" t="s">
-        <v>190</v>
-      </c>
-      <c r="J15" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="2">
-        <v>4</v>
-      </c>
-      <c r="D16" s="2">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>8</v>
-      </c>
-      <c r="H16" t="s">
-        <v>202</v>
-      </c>
-      <c r="I16" t="s">
-        <v>203</v>
-      </c>
-      <c r="J16" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="2">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2">
-        <v>24</v>
-      </c>
-      <c r="G17">
-        <v>9</v>
-      </c>
-      <c r="H17" t="s">
-        <v>205</v>
-      </c>
-      <c r="I17" t="s">
-        <v>206</v>
-      </c>
-      <c r="J17" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>10</v>
-      </c>
-      <c r="H18" t="s">
-        <v>208</v>
-      </c>
-      <c r="I18" t="s">
-        <v>206</v>
-      </c>
-      <c r="J18" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>11</v>
-      </c>
-      <c r="H19" t="s">
-        <v>210</v>
-      </c>
-      <c r="I19" t="s">
-        <v>206</v>
-      </c>
-      <c r="J19" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2">
-        <v>4</v>
-      </c>
-      <c r="G20">
-        <v>12</v>
-      </c>
-      <c r="H20" t="s">
-        <v>212</v>
-      </c>
-      <c r="I20" t="s">
-        <v>193</v>
-      </c>
-      <c r="J20" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2">
-        <v>2</v>
-      </c>
-      <c r="G21">
-        <v>13</v>
-      </c>
-      <c r="H21" t="s">
-        <v>214</v>
-      </c>
-      <c r="I21" t="s">
-        <v>193</v>
-      </c>
-      <c r="J21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <v>3</v>
-      </c>
-      <c r="G22">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
-        <v>216</v>
-      </c>
-      <c r="I22" t="s">
-        <v>193</v>
-      </c>
-      <c r="J22" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2">
-        <v>4</v>
-      </c>
-      <c r="G23">
-        <v>15</v>
-      </c>
-      <c r="H23" t="s">
-        <v>218</v>
-      </c>
-      <c r="I23" t="s">
-        <v>219</v>
-      </c>
-      <c r="J23" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="2">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2">
-        <v>14</v>
-      </c>
-      <c r="G24">
-        <v>16</v>
-      </c>
-      <c r="H24" t="s">
-        <v>221</v>
-      </c>
-      <c r="I24" t="s">
-        <v>222</v>
-      </c>
-      <c r="J24" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="2">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="2">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2">
-        <v>3</v>
-      </c>
-      <c r="G26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="2">
-        <v>4</v>
-      </c>
-      <c r="D27" s="2">
-        <v>13</v>
-      </c>
-      <c r="G27" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="2">
-        <v>2</v>
-      </c>
-      <c r="D28" s="2">
-        <v>9</v>
-      </c>
-      <c r="G28" t="s">
-        <v>180</v>
-      </c>
-      <c r="H28" t="s">
-        <v>45</v>
-      </c>
-      <c r="I28" t="s">
-        <v>181</v>
-      </c>
-      <c r="J28" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="2">
-        <v>3</v>
-      </c>
-      <c r="D29" s="2">
-        <v>16</v>
-      </c>
-      <c r="G29">
-        <v>17</v>
-      </c>
-      <c r="H29" t="s">
-        <v>225</v>
-      </c>
-      <c r="I29" t="s">
-        <v>193</v>
-      </c>
-      <c r="J29" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="2">
-        <v>2</v>
-      </c>
-      <c r="D30" s="2">
-        <v>7</v>
-      </c>
-      <c r="G30">
-        <v>18</v>
-      </c>
-      <c r="H30" t="s">
-        <v>227</v>
-      </c>
-      <c r="I30" t="s">
-        <v>193</v>
-      </c>
-      <c r="J30" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="2">
-        <v>3</v>
-      </c>
-      <c r="D31" s="2">
-        <v>8</v>
-      </c>
-      <c r="G31">
-        <v>19</v>
-      </c>
-      <c r="H31" t="s">
-        <v>229</v>
-      </c>
-      <c r="I31" t="s">
-        <v>193</v>
-      </c>
-      <c r="J31" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="2">
-        <v>6</v>
-      </c>
-      <c r="D32" s="2">
-        <v>9</v>
-      </c>
-      <c r="G32">
-        <v>20</v>
-      </c>
-      <c r="H32" t="s">
-        <v>231</v>
-      </c>
-      <c r="I32" t="s">
-        <v>232</v>
-      </c>
-      <c r="J32" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="2">
-        <v>4</v>
-      </c>
-      <c r="D33" s="2">
-        <v>14</v>
-      </c>
-      <c r="G33">
-        <v>21</v>
-      </c>
-      <c r="H33" t="s">
-        <v>234</v>
-      </c>
-      <c r="I33" t="s">
-        <v>232</v>
-      </c>
-      <c r="J33" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="2">
-        <v>3</v>
-      </c>
-      <c r="D34" s="2">
-        <v>7</v>
-      </c>
-      <c r="G34">
-        <v>22</v>
-      </c>
-      <c r="H34" t="s">
-        <v>236</v>
-      </c>
-      <c r="I34" t="s">
-        <v>219</v>
-      </c>
-      <c r="J34" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="2">
-        <v>2</v>
-      </c>
-      <c r="D35" s="2">
-        <v>4</v>
-      </c>
-      <c r="G35">
-        <v>23</v>
-      </c>
-      <c r="H35" t="s">
-        <v>238</v>
-      </c>
-      <c r="I35" t="s">
-        <v>239</v>
-      </c>
-      <c r="J35" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="2">
-        <v>7</v>
-      </c>
-      <c r="D36" s="2">
-        <v>22</v>
-      </c>
-      <c r="G36">
-        <v>24</v>
-      </c>
-      <c r="H36" t="s">
-        <v>241</v>
-      </c>
-      <c r="I36" t="s">
-        <v>187</v>
-      </c>
-      <c r="J36" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="G37">
-        <v>25</v>
-      </c>
-      <c r="H37" t="s">
-        <v>243</v>
-      </c>
-      <c r="I37" t="s">
-        <v>187</v>
-      </c>
-      <c r="J37" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2">
-        <v>107</v>
-      </c>
-      <c r="D38" s="2">
+      <c r="E70" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="20"/>
+      <c r="B71">
+        <v>55</v>
+      </c>
+      <c r="C71" t="s">
+        <v>314</v>
+      </c>
+      <c r="D71" t="s">
+        <v>315</v>
+      </c>
+      <c r="E71" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="B72">
+        <v>56</v>
+      </c>
+      <c r="C72" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="G38">
-        <v>26</v>
-      </c>
-      <c r="H38" t="s">
-        <v>245</v>
-      </c>
-      <c r="I38" t="s">
-        <v>246</v>
-      </c>
-      <c r="J38" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="G39">
-        <v>27</v>
-      </c>
-      <c r="H39" t="s">
-        <v>248</v>
-      </c>
-      <c r="I39" t="s">
-        <v>246</v>
-      </c>
-      <c r="J39" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="G40">
-        <v>28</v>
-      </c>
-      <c r="H40" t="s">
-        <v>250</v>
-      </c>
-      <c r="I40" t="s">
-        <v>251</v>
-      </c>
-      <c r="J40" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="G41">
-        <v>29</v>
-      </c>
-      <c r="H41" t="s">
+      <c r="D72" t="s">
         <v>253</v>
       </c>
-      <c r="I41" t="s">
-        <v>251</v>
-      </c>
-      <c r="J41" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="G42">
-        <v>30</v>
-      </c>
-      <c r="H42" t="s">
-        <v>255</v>
-      </c>
-      <c r="I42" t="s">
-        <v>256</v>
-      </c>
-      <c r="J42" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="G43">
-        <v>31</v>
-      </c>
-      <c r="H43" t="s">
-        <v>258</v>
-      </c>
-      <c r="I43" t="s">
-        <v>259</v>
-      </c>
-      <c r="J43" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="G44">
-        <v>32</v>
-      </c>
-      <c r="H44" t="s">
-        <v>261</v>
-      </c>
-      <c r="I44" t="s">
-        <v>259</v>
-      </c>
-      <c r="J44" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="G45">
-        <v>33</v>
-      </c>
-      <c r="H45" t="s">
-        <v>263</v>
-      </c>
-      <c r="I45" t="s">
-        <v>264</v>
-      </c>
-      <c r="J45" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="G46">
-        <v>34</v>
-      </c>
-      <c r="H46" t="s">
-        <v>266</v>
-      </c>
-      <c r="I46" t="s">
-        <v>264</v>
-      </c>
-      <c r="J46" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="G48" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="49" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G49" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="50" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G50" t="s">
-        <v>180</v>
-      </c>
-      <c r="H50" t="s">
-        <v>45</v>
-      </c>
-      <c r="I50" t="s">
-        <v>181</v>
-      </c>
-      <c r="J50" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="51" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G51">
-        <v>35</v>
-      </c>
-      <c r="H51" t="s">
-        <v>269</v>
-      </c>
-      <c r="I51" t="s">
-        <v>270</v>
-      </c>
-      <c r="J51" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="52" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G52">
-        <v>36</v>
-      </c>
-      <c r="H52" t="s">
-        <v>272</v>
-      </c>
-      <c r="I52" t="s">
-        <v>270</v>
-      </c>
-      <c r="J52" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="53" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G53">
-        <v>37</v>
-      </c>
-      <c r="H53" t="s">
-        <v>274</v>
-      </c>
-      <c r="I53" t="s">
-        <v>270</v>
-      </c>
-      <c r="J53" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="54" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G54">
-        <v>38</v>
-      </c>
-      <c r="H54" t="s">
-        <v>276</v>
-      </c>
-      <c r="I54" t="s">
-        <v>277</v>
-      </c>
-      <c r="J54" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="55" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G55">
-        <v>39</v>
-      </c>
-      <c r="H55" t="s">
-        <v>279</v>
-      </c>
-      <c r="I55" t="s">
-        <v>277</v>
-      </c>
-      <c r="J55" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="56" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G56">
-        <v>40</v>
-      </c>
-      <c r="H56" t="s">
-        <v>281</v>
-      </c>
-      <c r="I56" t="s">
-        <v>282</v>
-      </c>
-      <c r="J56" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="57" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G57">
-        <v>41</v>
-      </c>
-      <c r="H57" t="s">
-        <v>284</v>
-      </c>
-      <c r="I57" t="s">
-        <v>256</v>
-      </c>
-      <c r="J57" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="58" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G58">
-        <v>42</v>
-      </c>
-      <c r="H58" t="s">
-        <v>286</v>
-      </c>
-      <c r="I58" t="s">
-        <v>184</v>
-      </c>
-      <c r="J58" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="59" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G59">
-        <v>43</v>
-      </c>
-      <c r="H59" t="s">
-        <v>288</v>
-      </c>
-      <c r="I59" t="s">
-        <v>184</v>
-      </c>
-      <c r="J59" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="60" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G60">
-        <v>44</v>
-      </c>
-      <c r="H60" t="s">
-        <v>290</v>
-      </c>
-      <c r="I60" t="s">
-        <v>291</v>
-      </c>
-      <c r="J60" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="61" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G61">
-        <v>45</v>
-      </c>
-      <c r="H61" t="s">
-        <v>293</v>
-      </c>
-      <c r="I61" t="s">
-        <v>294</v>
-      </c>
-      <c r="J61" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="62" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G62">
-        <v>46</v>
-      </c>
-      <c r="H62" t="s">
-        <v>296</v>
-      </c>
-      <c r="I62" t="s">
-        <v>294</v>
-      </c>
-      <c r="J62" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="63" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G63">
-        <v>47</v>
-      </c>
-      <c r="H63" t="s">
-        <v>298</v>
-      </c>
-      <c r="I63" t="s">
-        <v>299</v>
-      </c>
-      <c r="J63" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="64" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G64">
-        <v>48</v>
-      </c>
-      <c r="H64" t="s">
-        <v>301</v>
-      </c>
-      <c r="I64" t="s">
-        <v>299</v>
-      </c>
-      <c r="J64" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="65" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G65">
-        <v>49</v>
-      </c>
-      <c r="H65" t="s">
-        <v>303</v>
-      </c>
-      <c r="I65" t="s">
-        <v>299</v>
-      </c>
-      <c r="J65" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="66" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G66">
-        <v>50</v>
-      </c>
-      <c r="H66" t="s">
-        <v>305</v>
-      </c>
-      <c r="I66" t="s">
-        <v>246</v>
-      </c>
-      <c r="J66" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="67" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G67">
-        <v>51</v>
-      </c>
-      <c r="H67" t="s">
-        <v>307</v>
-      </c>
-      <c r="I67" t="s">
-        <v>246</v>
-      </c>
-      <c r="J67" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="68" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G68">
-        <v>52</v>
-      </c>
-      <c r="H68" t="s">
-        <v>309</v>
-      </c>
-      <c r="I68" t="s">
-        <v>310</v>
-      </c>
-      <c r="J68" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="69" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G69">
-        <v>53</v>
-      </c>
-      <c r="H69" t="s">
-        <v>312</v>
-      </c>
-      <c r="I69" t="s">
-        <v>313</v>
-      </c>
-      <c r="J69" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="70" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G70">
-        <v>54</v>
-      </c>
-      <c r="H70" t="s">
-        <v>315</v>
-      </c>
-      <c r="I70" t="s">
-        <v>190</v>
-      </c>
-      <c r="J70" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="71" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G71">
-        <v>55</v>
-      </c>
-      <c r="H71" t="s">
-        <v>317</v>
-      </c>
-      <c r="I71" t="s">
+      <c r="E72" t="s">
         <v>318</v>
       </c>
-      <c r="J71" t="s">
+    </row>
+    <row r="73" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="20"/>
+      <c r="B73">
+        <v>57</v>
+      </c>
+      <c r="C73" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="72" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G72">
-        <v>56</v>
-      </c>
-      <c r="H72" t="s">
+      <c r="D73" t="s">
         <v>320</v>
       </c>
-      <c r="I72" t="s">
-        <v>256</v>
-      </c>
-      <c r="J72" t="s">
+      <c r="E73" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="73" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G73">
-        <v>57</v>
-      </c>
-      <c r="H73" t="s">
+    <row r="74" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="20"/>
+      <c r="B74">
+        <v>58</v>
+      </c>
+      <c r="C74" t="s">
         <v>322</v>
       </c>
-      <c r="I73" t="s">
+      <c r="D74" t="s">
+        <v>320</v>
+      </c>
+      <c r="E74" t="s">
         <v>323</v>
       </c>
-      <c r="J73" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="74" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G74">
-        <v>58</v>
-      </c>
-      <c r="H74" t="s">
-        <v>325</v>
-      </c>
-      <c r="I74" t="s">
-        <v>323</v>
-      </c>
-      <c r="J74" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="76" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G76" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="77" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G77" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="78" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G78" t="s">
-        <v>328</v>
-      </c>
-      <c r="H78" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="79" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G79" t="s">
-        <v>336</v>
-      </c>
-      <c r="H79" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="80" spans="7:10" x14ac:dyDescent="0.35">
-      <c r="G80" t="s">
-        <v>337</v>
-      </c>
-      <c r="H80" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="81" spans="7:8" x14ac:dyDescent="0.35">
-      <c r="G81" t="s">
-        <v>338</v>
-      </c>
-      <c r="H81" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="82" spans="7:8" x14ac:dyDescent="0.35">
-      <c r="G82" t="s">
-        <v>339</v>
-      </c>
-      <c r="H82" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="83" spans="7:8" x14ac:dyDescent="0.35">
-      <c r="G83" t="s">
-        <v>340</v>
-      </c>
-      <c r="H83" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="84" spans="7:8" x14ac:dyDescent="0.35">
-      <c r="G84" t="s">
-        <v>341</v>
-      </c>
-      <c r="H84" t="s">
-        <v>335</v>
-      </c>
-    </row>
+    </row>
+    <row r="75" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:D38" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="76" customWidth="1"/>
+    <col min="3" max="3" width="77" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
@@ -2935,181 +2939,193 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="D2" s="5">
-        <v>14.39</v>
+        <v>15.67</v>
       </c>
       <c r="E2" s="5">
-        <v>14.4</v>
+        <v>16.6175</v>
       </c>
       <c r="F2" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D3" s="5">
-        <v>12.72</v>
+        <v>15.6</v>
       </c>
       <c r="E3" s="5">
-        <v>14.27</v>
+        <v>15.6</v>
       </c>
       <c r="F3" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" s="5">
-        <v>12.45</v>
+        <v>15.51</v>
       </c>
       <c r="E4" s="5">
-        <v>14.32</v>
+        <v>15.51</v>
       </c>
       <c r="F4" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="D5" s="5">
-        <v>11.96</v>
+        <v>15.44</v>
       </c>
       <c r="E5" s="5">
-        <v>12.76</v>
+        <v>15.44</v>
       </c>
       <c r="F5" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="D6" s="5">
-        <v>13.89</v>
+        <v>15.21</v>
       </c>
       <c r="E6" s="5">
-        <v>13.89</v>
+        <v>16.872499999999999</v>
       </c>
       <c r="F6" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
+        <v>37</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="5">
+        <v>15.05</v>
+      </c>
+      <c r="E7" s="5">
+        <v>15.545</v>
+      </c>
+      <c r="F7" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="D8" s="5">
-        <v>12.57</v>
+        <v>15.04</v>
       </c>
       <c r="E8" s="5">
-        <v>13.52</v>
+        <v>15.04</v>
       </c>
       <c r="F8" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="5">
+        <v>15.02</v>
+      </c>
+      <c r="E9" s="5">
+        <v>15.02</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="D10" s="5">
-        <v>15.51</v>
+        <v>15.005000000000001</v>
       </c>
       <c r="E10" s="5">
-        <v>15.51</v>
+        <v>15.005000000000001</v>
       </c>
       <c r="F10" s="6">
         <v>1</v>
@@ -3117,133 +3133,139 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="D11" s="5">
-        <v>14.85</v>
+        <v>14.9</v>
       </c>
       <c r="E11" s="5">
         <v>14.9</v>
       </c>
       <c r="F11" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="5">
+        <v>14.85</v>
+      </c>
+      <c r="E12" s="5">
+        <v>14.9</v>
+      </c>
+      <c r="F12" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="D13" s="5">
-        <v>13.47</v>
+        <v>14.785</v>
       </c>
       <c r="E13" s="5">
-        <v>14.65</v>
+        <v>15.15</v>
       </c>
       <c r="F13" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D14" s="5">
-        <v>13.17</v>
+        <v>14.78</v>
       </c>
       <c r="E14" s="5">
-        <v>13.74</v>
+        <v>14.78</v>
       </c>
       <c r="F14" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="D15" s="5">
-        <v>13.61</v>
+        <v>14.63</v>
       </c>
       <c r="E15" s="5">
-        <v>14.27</v>
+        <v>14.8225</v>
       </c>
       <c r="F15" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="D16" s="5">
-        <v>13.49</v>
+        <v>14.63</v>
       </c>
       <c r="E16" s="5">
-        <v>14.27</v>
+        <v>14.63</v>
       </c>
       <c r="F16" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="D17" s="5">
-        <v>15.6</v>
+        <v>14.63</v>
       </c>
       <c r="E17" s="5">
-        <v>15.6</v>
+        <v>14.63</v>
       </c>
       <c r="F17" s="6">
         <v>1</v>
@@ -3251,161 +3273,179 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>62</v>
       </c>
       <c r="D18" s="5">
-        <v>13.73</v>
+        <v>14.54</v>
       </c>
       <c r="E18" s="5">
-        <v>13.73</v>
+        <v>14.54</v>
       </c>
       <c r="F18" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="D19" s="5">
-        <v>13.62</v>
+        <v>14.52</v>
       </c>
       <c r="E19" s="5">
-        <v>13.62</v>
+        <v>15.57</v>
       </c>
       <c r="F19" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C20" s="7" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D20" s="5">
-        <v>14.54</v>
+        <v>14.39</v>
       </c>
       <c r="E20" s="5">
-        <v>14.54</v>
+        <v>14.4</v>
       </c>
       <c r="F20" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D21" s="5">
-        <v>13.46</v>
+        <v>14.39</v>
       </c>
       <c r="E21" s="5">
-        <v>13.78</v>
+        <v>14.39</v>
       </c>
       <c r="F21" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="17">
+        <v>14.21</v>
+      </c>
+      <c r="E22" s="17">
+        <v>15.654999999999999</v>
+      </c>
+      <c r="F22" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>159</v>
+        <v>33</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="17">
+        <v>14.11</v>
+      </c>
+      <c r="E23" s="17">
+        <v>15.08</v>
+      </c>
+      <c r="F23" s="18">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="D24" s="5">
-        <v>13.9</v>
+        <v>14.085000000000001</v>
       </c>
       <c r="E24" s="5">
-        <v>14.06</v>
+        <v>14.73</v>
       </c>
       <c r="F24" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="D25" s="5">
-        <v>14.39</v>
+        <v>14.06</v>
       </c>
       <c r="E25" s="5">
-        <v>14.39</v>
+        <v>14.1</v>
       </c>
       <c r="F25" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D26" s="5">
-        <v>12.98</v>
+        <v>14.045</v>
       </c>
       <c r="E26" s="5">
-        <v>13.71</v>
+        <v>15.35</v>
       </c>
       <c r="F26" s="6">
         <v>2</v>
@@ -3413,53 +3453,59 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="5">
+        <v>14.01</v>
+      </c>
+      <c r="E27" s="5">
+        <v>15.32</v>
+      </c>
+      <c r="F27" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="D28" s="5">
-        <v>13.865</v>
+        <v>13.994999999999999</v>
       </c>
       <c r="E28" s="5">
-        <v>14.44</v>
+        <v>14.4</v>
       </c>
       <c r="F28" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D29" s="5">
-        <v>13.41</v>
+        <v>13.975</v>
       </c>
       <c r="E29" s="5">
-        <v>13.855</v>
+        <v>14.38</v>
       </c>
       <c r="F29" s="6">
         <v>4</v>
@@ -3467,315 +3513,339 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="D30" s="5">
-        <v>14.045</v>
+        <v>13.945</v>
       </c>
       <c r="E30" s="5">
-        <v>15.35</v>
+        <v>13.945</v>
       </c>
       <c r="F30" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C31" s="7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D31" s="5">
-        <v>15.02</v>
+        <v>13.9</v>
       </c>
       <c r="E31" s="5">
-        <v>15.02</v>
+        <v>14.06</v>
       </c>
       <c r="F31" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="D32" s="5">
-        <v>12.42</v>
+        <v>13.89</v>
       </c>
       <c r="E32" s="5">
-        <v>13.33</v>
+        <v>13.89</v>
       </c>
       <c r="F32" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="5">
+        <v>13.88</v>
+      </c>
+      <c r="E33" s="5">
+        <v>14.57</v>
+      </c>
+      <c r="F33" s="6">
+        <v>20</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="5">
+        <v>13.865</v>
+      </c>
+      <c r="E34" s="5">
+        <v>14.44</v>
+      </c>
+      <c r="F34" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="6"/>
+        <v>38</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" s="5">
+        <v>13.865</v>
+      </c>
+      <c r="E35" s="5">
+        <v>13.865</v>
+      </c>
+      <c r="F35" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D36" s="5">
-        <v>12.48</v>
+        <v>13.845000000000001</v>
       </c>
       <c r="E36" s="5">
-        <v>15.08</v>
+        <v>13.845000000000001</v>
       </c>
       <c r="F36" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D37" s="5">
-        <v>12.81</v>
+        <v>13.73</v>
       </c>
       <c r="E37" s="5">
-        <v>13.484999999999999</v>
+        <v>13.73</v>
       </c>
       <c r="F37" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="D38" s="5">
-        <v>12.775</v>
+        <v>13.65</v>
       </c>
       <c r="E38" s="5">
-        <v>13.435</v>
+        <v>14</v>
       </c>
       <c r="F38" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D39" s="5">
-        <v>12.74</v>
+        <v>13.63</v>
       </c>
       <c r="E39" s="5">
-        <v>13.37</v>
+        <v>13.914999999999999</v>
       </c>
       <c r="F39" s="6">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D40" s="5">
-        <v>12.54</v>
+        <v>13.62</v>
       </c>
       <c r="E40" s="5">
-        <v>13.05</v>
+        <v>13.62</v>
       </c>
       <c r="F40" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D41" s="5">
-        <v>12.37</v>
+        <v>13.61</v>
       </c>
       <c r="E41" s="5">
-        <v>12.37</v>
+        <v>14.27</v>
       </c>
       <c r="F41" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D42" s="5">
-        <v>14.785</v>
+        <v>13.605</v>
       </c>
       <c r="E42" s="5">
-        <v>15.15</v>
+        <v>13.855</v>
       </c>
       <c r="F42" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D43" s="5">
-        <v>13.63</v>
+        <v>13.605</v>
       </c>
       <c r="E43" s="5">
-        <v>13.914999999999999</v>
+        <v>13.605</v>
       </c>
       <c r="F43" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="D44" s="5">
-        <v>13.845000000000001</v>
+        <v>13.56</v>
       </c>
       <c r="E44" s="5">
-        <v>13.845000000000001</v>
+        <v>14.05</v>
       </c>
       <c r="F44" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" s="5">
+        <v>13.494999999999999</v>
+      </c>
+      <c r="E45" s="5">
+        <v>13.62</v>
+      </c>
+      <c r="F45" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D46" s="5">
-        <v>13.494999999999999</v>
+        <v>13.49</v>
       </c>
       <c r="E46" s="5">
-        <v>13.62</v>
+        <v>14.27</v>
       </c>
       <c r="F46" s="6">
         <v>2</v>
@@ -3783,219 +3853,219 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="D47" s="5">
-        <v>15.005000000000001</v>
+        <v>13.487500000000001</v>
       </c>
       <c r="E47" s="5">
-        <v>15.005000000000001</v>
+        <v>13.955</v>
       </c>
       <c r="F47" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D48" s="5">
-        <v>15.44</v>
+        <v>13.47</v>
       </c>
       <c r="E48" s="5">
-        <v>15.44</v>
+        <v>14.65</v>
       </c>
       <c r="F48" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="D49" s="5">
-        <v>14.9</v>
+        <v>13.46</v>
       </c>
       <c r="E49" s="5">
-        <v>14.9</v>
+        <v>13.78</v>
       </c>
       <c r="F49" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D50" s="5">
-        <v>14.78</v>
+        <v>13.46</v>
       </c>
       <c r="E50" s="5">
-        <v>14.78</v>
+        <v>13.984999999999999</v>
       </c>
       <c r="F50" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="D51" s="5">
-        <v>13.3</v>
+        <v>13.414999999999999</v>
       </c>
       <c r="E51" s="5">
-        <v>13.6</v>
+        <v>15.65</v>
       </c>
       <c r="F51" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D52" s="5">
-        <v>15.04</v>
+        <v>13.41</v>
       </c>
       <c r="E52" s="5">
-        <v>15.04</v>
+        <v>13.855</v>
       </c>
       <c r="F52" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D53" s="5">
-        <v>13.4</v>
+        <v>13.41</v>
       </c>
       <c r="E53" s="5">
-        <v>13.46</v>
+        <v>14.38</v>
       </c>
       <c r="F53" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="D54" s="5">
-        <v>13.39</v>
+        <v>13.404999999999999</v>
       </c>
       <c r="E54" s="5">
-        <v>13.39</v>
+        <v>13.7</v>
       </c>
       <c r="F54" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D55" s="5">
-        <v>13.975</v>
+        <v>13.4</v>
       </c>
       <c r="E55" s="5">
-        <v>14.38</v>
+        <v>13.46</v>
       </c>
       <c r="F55" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D56" s="5">
-        <v>13.605</v>
+        <v>13.39</v>
       </c>
       <c r="E56" s="5">
-        <v>13.855</v>
+        <v>13.39</v>
       </c>
       <c r="F56" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D57" s="5">
-        <v>13.41</v>
+        <v>13.3</v>
       </c>
       <c r="E57" s="5">
-        <v>14.38</v>
+        <v>13.6</v>
       </c>
       <c r="F57" s="6">
         <v>3</v>
@@ -4003,73 +4073,79 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="D58" s="5">
-        <v>13.88</v>
+        <v>13.295</v>
       </c>
       <c r="E58" s="5">
-        <v>14.57</v>
+        <v>13.395</v>
       </c>
       <c r="F58" s="6">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="D59" s="5">
-        <v>14.63</v>
+        <v>13.285</v>
       </c>
       <c r="E59" s="5">
-        <v>14.8225</v>
+        <v>13.62</v>
       </c>
       <c r="F59" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="5">
+        <v>13.244999999999999</v>
+      </c>
+      <c r="E60" s="5">
+        <v>15.305</v>
+      </c>
+      <c r="F60" s="6">
+        <v>10</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="D61" s="5">
-        <v>12.52</v>
+        <v>13.175000000000001</v>
       </c>
       <c r="E61" s="5">
-        <v>12.75</v>
+        <v>13.39</v>
       </c>
       <c r="F61" s="6">
         <v>2</v>
@@ -4077,33 +4153,39 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="5">
+        <v>13.17</v>
+      </c>
+      <c r="E62" s="5">
+        <v>13.74</v>
+      </c>
+      <c r="F62" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D63" s="5">
-        <v>12.32</v>
+        <v>13.115</v>
       </c>
       <c r="E63" s="5">
-        <v>12.33</v>
+        <v>13.21</v>
       </c>
       <c r="F63" s="6">
         <v>2</v>
@@ -4111,59 +4193,59 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="D64" s="5">
-        <v>13.115</v>
+        <v>13.06</v>
       </c>
       <c r="E64" s="5">
-        <v>13.21</v>
+        <v>13.574999999999999</v>
       </c>
       <c r="F64" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D65" s="5">
-        <v>13.46</v>
+        <v>12.984999999999999</v>
       </c>
       <c r="E65" s="5">
-        <v>13.984999999999999</v>
+        <v>13.15</v>
       </c>
       <c r="F65" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" s="5">
-        <v>12.93</v>
+        <v>12.984999999999999</v>
       </c>
       <c r="E66" s="5">
-        <v>13.63</v>
+        <v>13.77</v>
       </c>
       <c r="F66" s="6">
         <v>2</v>
@@ -4171,19 +4253,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="D67" s="5">
-        <v>14.21</v>
+        <v>12.98</v>
       </c>
       <c r="E67" s="5">
-        <v>15.654999999999999</v>
+        <v>13.71</v>
       </c>
       <c r="F67" s="6">
         <v>2</v>
@@ -4191,19 +4273,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D68" s="5">
-        <v>12.984999999999999</v>
+        <v>12.93</v>
       </c>
       <c r="E68" s="5">
-        <v>13.15</v>
+        <v>13.63</v>
       </c>
       <c r="F68" s="6">
         <v>2</v>
@@ -4211,79 +4293,79 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D69" s="5">
-        <v>12.984999999999999</v>
+        <v>12.914999999999999</v>
       </c>
       <c r="E69" s="5">
-        <v>13.77</v>
+        <v>13.414999999999999</v>
       </c>
       <c r="F69" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="D70" s="5">
-        <v>12.615</v>
+        <v>12.855</v>
       </c>
       <c r="E70" s="5">
-        <v>13.17</v>
+        <v>13.07</v>
       </c>
       <c r="F70" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="D71" s="5">
-        <v>11.27</v>
+        <v>12.81</v>
       </c>
       <c r="E71" s="5">
-        <v>12.86</v>
+        <v>13.484999999999999</v>
       </c>
       <c r="F71" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="D72" s="5">
-        <v>12.25</v>
+        <v>12.79</v>
       </c>
       <c r="E72" s="5">
-        <v>12.36</v>
+        <v>13.47</v>
       </c>
       <c r="F72" s="6">
         <v>3</v>
@@ -4291,705 +4373,711 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="D73" s="5">
-        <v>12.035</v>
+        <v>12.775</v>
       </c>
       <c r="E73" s="5">
-        <v>12.08</v>
+        <v>13.435</v>
       </c>
       <c r="F73" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="6"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D74" s="5">
+        <v>12.74</v>
+      </c>
+      <c r="E74" s="5">
+        <v>13.37</v>
+      </c>
+      <c r="F74" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="6"/>
+        <v>31</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D75" s="5">
+        <v>12.74</v>
+      </c>
+      <c r="E75" s="5">
+        <v>12.93</v>
+      </c>
+      <c r="F75" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D76" s="5">
+        <v>12.72</v>
+      </c>
+      <c r="E76" s="5">
+        <v>14.27</v>
+      </c>
+      <c r="F76" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="D77" s="5">
-        <v>12.525</v>
+        <v>12.66</v>
       </c>
       <c r="E77" s="5">
-        <v>12.525</v>
+        <v>13.095000000000001</v>
       </c>
       <c r="F77" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D78" s="5">
-        <v>12.74</v>
+        <v>12.615</v>
       </c>
       <c r="E78" s="5">
-        <v>12.93</v>
+        <v>13.17</v>
       </c>
       <c r="F78" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="D79" s="5">
-        <v>12.914999999999999</v>
+        <v>12.57</v>
       </c>
       <c r="E79" s="5">
-        <v>13.414999999999999</v>
+        <v>13.52</v>
       </c>
       <c r="F79" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="D80" s="5">
-        <v>12.34</v>
+        <v>12.57</v>
       </c>
       <c r="E80" s="5">
-        <v>12.34</v>
+        <v>12.57</v>
       </c>
       <c r="F80" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D81" s="5">
-        <v>11.85</v>
+        <v>12.55</v>
       </c>
       <c r="E81" s="5">
-        <v>12.574999999999999</v>
+        <v>13.68</v>
       </c>
       <c r="F81" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="D82" s="5">
-        <v>12.135</v>
+        <v>12.54</v>
       </c>
       <c r="E82" s="5">
-        <v>12.35</v>
+        <v>13.05</v>
       </c>
       <c r="F82" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D83" s="5">
-        <v>13.285</v>
+        <v>12.525</v>
       </c>
       <c r="E83" s="5">
-        <v>13.62</v>
+        <v>12.525</v>
       </c>
       <c r="F83" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D84" s="5">
-        <v>14.085000000000001</v>
+        <v>12.52</v>
       </c>
       <c r="E84" s="5">
-        <v>14.73</v>
+        <v>12.75</v>
       </c>
       <c r="F84" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D85" s="5">
-        <v>13.994999999999999</v>
+        <v>12.484999999999999</v>
       </c>
       <c r="E85" s="5">
-        <v>14.4</v>
+        <v>12.484999999999999</v>
       </c>
       <c r="F85" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="D86" s="5">
-        <v>14.11</v>
+        <v>12.48</v>
       </c>
       <c r="E86" s="5">
         <v>15.08</v>
       </c>
       <c r="F86" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="D87" s="5">
-        <v>15.67</v>
+        <v>12.45</v>
       </c>
       <c r="E87" s="5">
-        <v>16.6175</v>
+        <v>14.32</v>
       </c>
       <c r="F87" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D88" s="5">
+        <v>12.44</v>
+      </c>
+      <c r="E88" s="5">
+        <v>13.43</v>
+      </c>
+      <c r="F88" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="D89" s="5">
-        <v>14.52</v>
+        <v>12.42</v>
       </c>
       <c r="E89" s="5">
-        <v>15.57</v>
+        <v>13.33</v>
       </c>
       <c r="F89" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="6"/>
+        <v>39</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D90" s="5">
+        <v>12.395</v>
+      </c>
+      <c r="E90" s="5">
+        <v>12.82</v>
+      </c>
+      <c r="F90" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C91" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="6"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D91" s="5">
+        <v>12.37</v>
+      </c>
+      <c r="E91" s="5">
+        <v>12.37</v>
+      </c>
+      <c r="F91" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D92" s="5">
-        <v>12.55</v>
+        <v>12.34</v>
       </c>
       <c r="E92" s="5">
-        <v>13.68</v>
+        <v>12.34</v>
       </c>
       <c r="F92" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D93" s="5">
-        <v>13.244999999999999</v>
+        <v>12.32</v>
       </c>
       <c r="E93" s="5">
-        <v>15.305</v>
+        <v>12.33</v>
       </c>
       <c r="F93" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D94" s="5">
-        <v>13.06</v>
+        <v>12.265000000000001</v>
       </c>
       <c r="E94" s="5">
-        <v>13.574999999999999</v>
+        <v>13.12</v>
       </c>
       <c r="F94" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D95" s="5">
-        <v>12.265000000000001</v>
+        <v>12.25</v>
       </c>
       <c r="E95" s="5">
-        <v>13.12</v>
+        <v>12.36</v>
       </c>
       <c r="F95" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D96" s="5">
-        <v>12.484999999999999</v>
+        <v>12.135</v>
       </c>
       <c r="E96" s="5">
-        <v>12.484999999999999</v>
+        <v>12.35</v>
       </c>
       <c r="F96" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="D97" s="5">
-        <v>12.44</v>
+        <v>12.035</v>
       </c>
       <c r="E97" s="5">
-        <v>13.43</v>
+        <v>12.08</v>
       </c>
       <c r="F97" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="D98" s="5">
-        <v>13.56</v>
+        <v>11.96</v>
       </c>
       <c r="E98" s="5">
-        <v>14.05</v>
+        <v>12.76</v>
       </c>
       <c r="F98" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D99" s="5">
-        <v>14.06</v>
+        <v>11.855</v>
       </c>
       <c r="E99" s="5">
-        <v>14.1</v>
+        <v>13.13</v>
       </c>
       <c r="F99" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="D100" s="5">
-        <v>15.05</v>
+        <v>11.85</v>
       </c>
       <c r="E100" s="5">
-        <v>15.545</v>
+        <v>12.574999999999999</v>
       </c>
       <c r="F100" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C101" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D101" s="5">
+        <v>11.425000000000001</v>
+      </c>
+      <c r="E101" s="5">
+        <v>11.425000000000001</v>
+      </c>
+      <c r="F101" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C102" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D102" s="5">
+        <v>11.27</v>
+      </c>
+      <c r="E102" s="5">
+        <v>12.86</v>
+      </c>
+      <c r="F102" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="103" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D103" s="5">
-        <v>14.63</v>
-      </c>
-      <c r="E103" s="5">
-        <v>14.63</v>
-      </c>
-      <c r="F103" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="6"/>
+    </row>
+    <row r="104" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D104" s="5">
-        <v>13.295</v>
-      </c>
-      <c r="E104" s="5">
-        <v>13.395</v>
-      </c>
-      <c r="F104" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="6"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="D105" s="5">
-        <v>13.605</v>
-      </c>
-      <c r="E105" s="5">
-        <v>13.605</v>
-      </c>
-      <c r="F105" s="6">
-        <v>1</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="6"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D106" s="5">
-        <v>13.865</v>
-      </c>
-      <c r="E106" s="5">
-        <v>13.865</v>
-      </c>
-      <c r="F106" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D106" s="16"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="6"/>
+    </row>
+    <row r="107" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D107" s="5">
-        <v>13.945</v>
-      </c>
-      <c r="E107" s="5">
-        <v>13.945</v>
-      </c>
-      <c r="F107" s="6">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D107" s="16"/>
+      <c r="E107" s="16"/>
+      <c r="F107" s="6"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D108" s="5">
-        <v>13.487500000000001</v>
-      </c>
-      <c r="E108" s="5">
-        <v>13.955</v>
-      </c>
-      <c r="F108" s="6">
-        <v>3</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="6"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D109" s="5">
-        <v>12.395</v>
-      </c>
-      <c r="E109" s="5">
-        <v>12.82</v>
-      </c>
-      <c r="F109" s="6">
-        <v>3</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="6"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
@@ -4997,282 +5085,212 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D111" s="5">
-        <v>13.414999999999999</v>
-      </c>
-      <c r="E111" s="5">
-        <v>15.65</v>
-      </c>
-      <c r="F111" s="6">
-        <v>5</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="6"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D112" s="5">
-        <v>12.855</v>
-      </c>
-      <c r="E112" s="5">
-        <v>13.07</v>
-      </c>
-      <c r="F112" s="6">
-        <v>3</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="6"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D113" s="5">
-        <v>12.79</v>
-      </c>
-      <c r="E113" s="5">
-        <v>13.47</v>
-      </c>
-      <c r="F113" s="6">
-        <v>3</v>
-      </c>
+      <c r="C113" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D113" s="5"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="6"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D114" s="5">
-        <v>13.175000000000001</v>
-      </c>
-      <c r="E114" s="5">
-        <v>13.39</v>
-      </c>
-      <c r="F114" s="6">
-        <v>2</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D114" s="5"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="6"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D115" s="5">
-        <v>13.404999999999999</v>
-      </c>
-      <c r="E115" s="5">
-        <v>13.7</v>
-      </c>
-      <c r="F115" s="6">
-        <v>2</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D115" s="5"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="6"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D116" s="5">
-        <v>15.21</v>
-      </c>
-      <c r="E116" s="5">
-        <v>16.872499999999999</v>
-      </c>
-      <c r="F116" s="6">
-        <v>3</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D116" s="5"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="6"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D117" s="5">
-        <v>12.66</v>
-      </c>
-      <c r="E117" s="5">
-        <v>13.095000000000001</v>
-      </c>
-      <c r="F117" s="6">
-        <v>2</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="6"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D118" s="5">
-        <v>13.65</v>
-      </c>
-      <c r="E118" s="5">
-        <v>14</v>
-      </c>
-      <c r="F118" s="6">
-        <v>2</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D118" s="5"/>
+      <c r="E118" s="5"/>
+      <c r="F118" s="6"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D119" s="5">
-        <v>14.63</v>
-      </c>
-      <c r="E119" s="5">
-        <v>14.63</v>
-      </c>
-      <c r="F119" s="6">
-        <v>1</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D119" s="5"/>
+      <c r="E119" s="5"/>
+      <c r="F119" s="6"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D120" s="5">
-        <v>11.425000000000001</v>
-      </c>
-      <c r="E120" s="5">
-        <v>11.425000000000001</v>
-      </c>
-      <c r="F120" s="6">
-        <v>1</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D120" s="5"/>
+      <c r="E120" s="5"/>
+      <c r="F120" s="6"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D121" s="5">
-        <v>12.57</v>
-      </c>
-      <c r="E121" s="5">
-        <v>12.57</v>
-      </c>
-      <c r="F121" s="6">
-        <v>2</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D121" s="5"/>
+      <c r="E121" s="5"/>
+      <c r="F121" s="6"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D122" s="5">
-        <v>14.01</v>
-      </c>
-      <c r="E122" s="5">
-        <v>15.32</v>
-      </c>
-      <c r="F122" s="6">
-        <v>2</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D122" s="5"/>
+      <c r="E122" s="5"/>
+      <c r="F122" s="6"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D123" s="5">
-        <v>11.855</v>
-      </c>
-      <c r="E123" s="5">
-        <v>13.13</v>
-      </c>
-      <c r="F123" s="6">
-        <v>3</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D123" s="5"/>
+      <c r="E123" s="5"/>
+      <c r="F123" s="6"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>177</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="F124" s="6"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F125" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F106" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:F124" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F124">
+      <sortCondition descending="1" ref="D1:D106"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5292,27 +5310,27 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" s="5">
         <v>13.11</v>
@@ -5330,7 +5348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5350,27 +5368,27 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D2" s="5">
         <v>14.39</v>
@@ -5384,13 +5402,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D3" s="5">
         <v>12.72</v>
@@ -5404,13 +5422,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4" s="5">
         <v>12.45</v>
@@ -5424,13 +5442,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D5" s="5">
         <v>11.96</v>
@@ -5444,13 +5462,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D6" s="5">
         <v>13.89</v>
@@ -5464,13 +5482,13 @@
     </row>
     <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -5478,13 +5496,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D8" s="5">
         <v>12.57</v>
@@ -5498,13 +5516,13 @@
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -5512,13 +5530,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D10" s="5">
         <v>15.51</v>
@@ -5532,13 +5550,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D11" s="5">
         <v>14.85</v>
@@ -5552,13 +5570,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -5566,13 +5584,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D13" s="5">
         <v>13.47</v>
@@ -5586,13 +5604,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" s="5">
         <v>13.17</v>
@@ -5606,13 +5624,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" s="5">
         <v>13.61</v>
@@ -5626,13 +5644,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D16" s="5">
         <v>13.49</v>
@@ -5646,13 +5664,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D17" s="5">
         <v>15.6</v>
@@ -5666,13 +5684,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D18" s="5">
         <v>13.73</v>
@@ -5686,13 +5704,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D19" s="5">
         <v>13.62</v>
@@ -5706,13 +5724,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D20" s="5">
         <v>14.54</v>
@@ -5726,13 +5744,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D21" s="5">
         <v>13.46</v>
@@ -5746,24 +5764,24 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -5772,7 +5790,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5792,27 +5810,27 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D2" s="5">
         <v>13.9</v>
@@ -5826,13 +5844,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" s="5">
         <v>14.39</v>
@@ -5846,13 +5864,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D4" s="5">
         <v>12.98</v>
@@ -5866,13 +5884,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -5880,13 +5898,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D6" s="5">
         <v>13.865</v>
@@ -5900,13 +5918,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5">
         <v>13.41</v>
@@ -5920,13 +5938,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D8" s="5">
         <v>14.045</v>
@@ -5940,13 +5958,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" s="5">
         <v>15.02</v>
@@ -5960,13 +5978,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D10" s="5">
         <v>12.42</v>
@@ -5980,13 +5998,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -5994,13 +6012,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -6008,13 +6026,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -6022,13 +6040,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" s="5">
         <v>12.48</v>
@@ -6042,13 +6060,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D15" s="5">
         <v>12.81</v>
@@ -6062,13 +6080,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D16" s="5">
         <v>12.775</v>
@@ -6082,13 +6100,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D17" s="5">
         <v>12.74</v>
@@ -6102,13 +6120,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D18" s="5">
         <v>12.54</v>
@@ -6122,13 +6140,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D19" s="5">
         <v>12.37</v>
@@ -6142,13 +6160,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D20" s="5">
         <v>14.785</v>
@@ -6162,13 +6180,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D21" s="5">
         <v>13.63</v>
@@ -6182,13 +6200,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D22" s="5">
         <v>13.845000000000001</v>
@@ -6202,13 +6220,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -6216,13 +6234,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D24" s="5">
         <v>13.494999999999999</v>
@@ -6236,13 +6254,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D25" s="5">
         <v>15.005000000000001</v>
@@ -6256,13 +6274,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D26" s="5">
         <v>15.44</v>
@@ -6276,13 +6294,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" s="5">
         <v>14.9</v>
@@ -6296,13 +6314,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D28" s="5">
         <v>14.78</v>
@@ -6316,13 +6334,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D29" s="5">
         <v>13.3</v>
@@ -6336,13 +6354,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D30" s="5">
         <v>15.04</v>
@@ -6356,13 +6374,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D31" s="5">
         <v>13.4</v>
@@ -6376,13 +6394,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D32" s="5">
         <v>13.39</v>
@@ -6396,13 +6414,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D33" s="5">
         <v>13.975</v>
@@ -6416,13 +6434,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D34" s="5">
         <v>13.605</v>
@@ -6436,13 +6454,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D35" s="5">
         <v>13.41</v>
@@ -6456,13 +6474,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D36" s="5">
         <v>13.88</v>
@@ -6476,13 +6494,13 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D37" s="5">
         <v>14.14</v>
@@ -6500,7 +6518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6520,27 +6538,27 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" s="5">
         <v>13.34</v>
@@ -6558,7 +6576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6578,27 +6596,27 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D2" s="5">
         <v>14.63</v>
@@ -6612,13 +6630,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C3" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -6626,13 +6644,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D4" s="5">
         <v>12.52</v>
@@ -6646,13 +6664,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -6660,13 +6678,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D6" s="5">
         <v>12.32</v>
@@ -6680,13 +6698,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D7" s="5">
         <v>13.115</v>
@@ -6700,13 +6718,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" s="5">
         <v>13.46</v>
@@ -6720,13 +6738,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" s="5">
         <v>12.93</v>
@@ -6740,13 +6758,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D10" s="5">
         <v>14.21</v>
@@ -6760,13 +6778,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D11" s="5">
         <v>12.984999999999999</v>
@@ -6780,13 +6798,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D12" s="5">
         <v>12.984999999999999</v>
@@ -6800,13 +6818,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" s="5">
         <v>12.615</v>
@@ -6820,13 +6838,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D14" s="5">
         <v>11.27</v>
@@ -6840,13 +6858,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D15" s="5">
         <v>12.25</v>
@@ -6860,13 +6878,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D16" s="5">
         <v>12.035</v>
@@ -6880,13 +6898,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D17" s="5">
         <v>14.65</v>
@@ -6900,13 +6918,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -6914,13 +6932,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -6928,13 +6946,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -6942,13 +6960,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D21" s="5">
         <v>12.525</v>
@@ -6962,13 +6980,13 @@
     </row>
     <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D22" s="5">
         <v>12.74</v>
@@ -6982,13 +7000,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D23" s="5">
         <v>12.914999999999999</v>
@@ -7002,13 +7020,13 @@
     </row>
     <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D24" s="5">
         <v>12.34</v>
@@ -7022,13 +7040,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D25" s="5">
         <v>11.85</v>
@@ -7042,13 +7060,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D26" s="5">
         <v>12.135</v>
@@ -7062,13 +7080,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D27" s="5">
         <v>13.285</v>
@@ -7082,13 +7100,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" s="5">
         <v>14.085000000000001</v>
@@ -7102,13 +7120,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D29" s="5">
         <v>13.994999999999999</v>
@@ -7122,13 +7140,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D30" s="5">
         <v>14.11</v>
@@ -7142,13 +7160,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D31" s="5">
         <v>15.67</v>
@@ -7162,13 +7180,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -7176,13 +7194,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D33" s="5">
         <v>14.52</v>
@@ -7196,13 +7214,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -7210,13 +7228,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -7224,13 +7242,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D36" s="5">
         <v>12.55</v>
@@ -7244,13 +7262,13 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D37" s="5">
         <v>13.244999999999999</v>
@@ -7264,13 +7282,13 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D38" s="5">
         <v>13.06</v>
@@ -7284,13 +7302,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D39" s="5">
         <v>12.265000000000001</v>
@@ -7304,13 +7322,13 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D40" s="5">
         <v>12.484999999999999</v>
@@ -7324,13 +7342,13 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D41" s="5">
         <v>12.44</v>
@@ -7344,13 +7362,13 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D42" s="5">
         <v>13.56</v>
@@ -7364,13 +7382,13 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D43" s="5">
         <v>14.06</v>
@@ -7384,13 +7402,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D44" s="5">
         <v>15.05</v>
@@ -7404,13 +7422,13 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -7418,13 +7436,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -7432,13 +7450,13 @@
     </row>
     <row r="47" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D47" s="5">
         <v>14.63</v>
@@ -7452,13 +7470,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D48" s="5">
         <v>13.295</v>
@@ -7472,13 +7490,13 @@
     </row>
     <row r="49" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D49" s="5">
         <v>13.605</v>
@@ -7492,13 +7510,13 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D50" s="5">
         <v>13.865</v>
@@ -7512,13 +7530,13 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D51" s="5">
         <v>13.945</v>
@@ -7532,13 +7550,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D52" s="5">
         <v>13.487500000000001</v>
@@ -7552,13 +7570,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D53" s="5">
         <v>12.395</v>
@@ -7572,13 +7590,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
@@ -7586,13 +7604,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D55" s="5">
         <v>13.414999999999999</v>
@@ -7606,13 +7624,13 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D56" s="5">
         <v>12.855</v>
@@ -7626,13 +7644,13 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D57" s="5">
         <v>12.79</v>
@@ -7646,13 +7664,13 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D58" s="5">
         <v>13.175000000000001</v>
@@ -7666,13 +7684,13 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D59" s="5">
         <v>13.404999999999999</v>
@@ -7686,13 +7704,13 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D60" s="5">
         <v>15.21</v>
@@ -7706,13 +7724,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D61" s="5">
         <v>12.66</v>
@@ -7726,13 +7744,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D62" s="5">
         <v>13.65</v>
@@ -7746,13 +7764,13 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D63" s="5">
         <v>14.63</v>
@@ -7766,13 +7784,13 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D64" s="5">
         <v>11.425000000000001</v>
@@ -7786,13 +7804,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D65" s="5">
         <v>12.57</v>
@@ -7806,13 +7824,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D66" s="5">
         <v>13.345000000000001</v>
@@ -7826,13 +7844,13 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D67" s="5">
         <v>14.01</v>
@@ -7846,13 +7864,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D68" s="5">
         <v>12.88</v>
@@ -7866,13 +7884,13 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D69" s="5">
         <v>11.855</v>
@@ -7886,13 +7904,13 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/OUT_25-26_M2_BM_universites.xlsx
+++ b/OUT_25-26_M2_BM_universites.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coulono\Downloads\Navigo - perso\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D41000B-46F1-4427-811F-07176CAB8709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F76A9D-A721-487A-AC4F-574BC52987BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13785" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="8" r:id="rId1"/>
@@ -1274,7 +1274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1303,36 +1303,35 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1640,189 +1639,189 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8D01D8-A348-4A3C-A33B-1505E738259C}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="141.6328125" customWidth="1"/>
+    <col min="1" max="1" width="39.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="141.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:2" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>363</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="B2" s="29" t="str">
+      <c r="B2" s="28" t="str">
         <f>_xlfn.XLOOKUP(A2,Tierlist!C:C,Tierlist!A:A)</f>
         <v>Maitreclasse</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="B3" s="29" t="str">
+      <c r="B3" s="28" t="str">
         <f>_xlfn.XLOOKUP(A3,Tierlist!C:C,Tierlist!A:A)</f>
         <v>semble plutôt banger ça, beaucoup de cours quantitatifs, visiblement pas de limite sur ce qu'on peut prendre</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="29" t="str">
+      <c r="B4" s="28" t="str">
         <f>_xlfn.XLOOKUP(A4,Tierlist!C:C,Tierlist!A:A)</f>
         <v>cours vraiment bien (à la fois quantitatif, mais aussi bcp de data), à voir acceptation edhec ("it is not possible to specialize in Economics during this exchange and Finance courses are generally not accepted for credit transfer except courses related to the fields of Accounting and Auditing")</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="28" t="str">
         <f>_xlfn.XLOOKUP(A5,Tierlist!C:C,Tierlist!A:A)</f>
         <v>choix de cours plutôt large et bien adapté, top cours : Asset management, Money, banking &amp; financial markets, time series analysis &amp; machine learning</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="23" t="s">
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="B6" s="29" t="str">
+      <c r="B6" s="28" t="str">
         <f>_xlfn.XLOOKUP(A6,Tierlist!C:C,Tierlist!A:A)</f>
         <v>vraiment bon choix, cours pertinents : Derivatives, neural networks for Eco and Finance, advanced monetary policy, macroeconometrics, time series analysis,asset pricing, financial econometrics</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="B7" s="29" t="str">
+      <c r="B7" s="28" t="str">
         <f>_xlfn.XLOOKUP(A7,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">Big, cours vraiment pertinents, à voir éligibilité edhec </v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="23" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="B8" s="29" t="str">
+      <c r="B8" s="28" t="str">
         <f>_xlfn.XLOOKUP(A8,Tierlist!C:C,Tierlist!A:A)</f>
         <v>Cours vraiment bien sur campus bruxelles (est ce que je veux aller dans cacaville Bruxelles : non)</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="23" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>287</v>
       </c>
-      <c r="B9" s="29" t="str">
+      <c r="B9" s="28" t="str">
         <f>_xlfn.XLOOKUP(A9,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">derivatives dispo : maitreclassique </v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="23" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="B10" s="29" t="str">
+      <c r="B10" s="28" t="str">
         <f>_xlfn.XLOOKUP(A10,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">idem que WHU koblenz : mid mais reste ok </v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="23" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B11" s="29" t="str">
+      <c r="B11" s="28" t="str">
         <f>_xlfn.XLOOKUP(A11,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">chine, sinon pas de bon programme </v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" s="20"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="27" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
         <v>365</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="B14" s="29" t="str">
+      <c r="B14" s="28" t="str">
         <f>_xlfn.XLOOKUP(A14,Tierlist!C:C,Tierlist!A:A)</f>
         <v>échange cool, cours absolument réduits a néant a cause edhec</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="B15" s="29" t="str">
+      <c r="B15" s="28" t="str">
         <f>_xlfn.XLOOKUP(A15,Tierlist!C:C,Tierlist!A:A)</f>
         <v>2 cours intéressants, le reste pue</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="29" t="str">
+      <c r="B16" s="28" t="str">
         <f>_xlfn.XLOOKUP(A16,Tierlist!C:C,Tierlist!A:A)</f>
         <v>programmes pas trop clairs car sont présentés en 2ans, mais programme Msc economic and finance - Advanced eco and finance plutôt pas mal au global</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="25" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="29" t="str">
+      <c r="B17" s="28" t="str">
         <f>_xlfn.XLOOKUP(A17,Tierlist!C:C,Tierlist!A:A)</f>
         <v>idem, cours interessants mais pascompris ce qu'on avait le droit de prendre</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="25" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="B18" s="29" t="str">
+      <c r="B18" s="28" t="str">
         <f>_xlfn.XLOOKUP(A18,Tierlist!C:C,Tierlist!A:A)</f>
         <v>pas de derivatives, pas d'asset pricing, mais cours quantitatifs quand même</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="25" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="24" t="s">
         <v>263</v>
       </c>
-      <c r="B19" s="29" t="str">
+      <c r="B19" s="28" t="str">
         <f>_xlfn.XLOOKUP(A19,Tierlist!C:C,Tierlist!A:A)</f>
         <v>rien pané au choix des cours, mais y a des très bons cours quantitatifs</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="B20" s="29" t="str">
+      <c r="B20" s="28" t="str">
         <f>_xlfn.XLOOKUP(A20,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">MSc in Information Science and Technology Management why not, sinon pas ed choses pour front </v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="25" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="24" t="s">
         <v>281</v>
       </c>
-      <c r="B21" s="29" t="str">
+      <c r="B21" s="28" t="str">
         <f>_xlfn.XLOOKUP(A21,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">chine, sinon pas de bon programme </v>
       </c>
@@ -1835,16 +1834,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E84"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="74.7265625" customWidth="1"/>
-    <col min="2" max="2" width="6.36328125" customWidth="1"/>
-    <col min="3" max="3" width="55.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="81.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="74.77734375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="55.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="81.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>324</v>
       </c>
@@ -1852,8 +1851,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>177</v>
       </c>
@@ -1867,7 +1866,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>325</v>
       </c>
@@ -1884,7 +1883,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>326</v>
       </c>
@@ -1901,7 +1900,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>331</v>
       </c>
@@ -1918,7 +1917,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>329</v>
       </c>
@@ -1935,7 +1934,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>328</v>
       </c>
@@ -1952,19 +1951,19 @@
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20"/>
     </row>
-    <row r="11" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20"/>
       <c r="B11" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20"/>
     </row>
-    <row r="13" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20"/>
       <c r="B13" t="s">
         <v>177</v>
@@ -1979,7 +1978,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>330</v>
       </c>
@@ -1996,7 +1995,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>327</v>
       </c>
@@ -2013,14 +2012,14 @@
         <v>198</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>332</v>
       </c>
       <c r="B16">
         <v>8</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="14" t="s">
         <v>199</v>
       </c>
       <c r="D16" t="s">
@@ -2030,7 +2029,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>333</v>
       </c>
@@ -2047,7 +2046,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>325</v>
       </c>
@@ -2064,7 +2063,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>334</v>
       </c>
@@ -2081,7 +2080,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="20" t="s">
         <v>335</v>
       </c>
@@ -2098,7 +2097,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
         <v>336</v>
       </c>
@@ -2115,7 +2114,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>337</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="20" t="s">
         <v>338</v>
       </c>
@@ -2149,7 +2148,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
         <v>339</v>
       </c>
@@ -2166,19 +2165,19 @@
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20"/>
     </row>
-    <row r="26" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20"/>
       <c r="B26" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="20"/>
     </row>
-    <row r="28" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20"/>
       <c r="B28" t="s">
         <v>177</v>
@@ -2193,7 +2192,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20" t="s">
         <v>340</v>
       </c>
@@ -2210,7 +2209,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20" t="s">
         <v>341</v>
       </c>
@@ -2227,7 +2226,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20" t="s">
         <v>342</v>
       </c>
@@ -2244,14 +2243,14 @@
         <v>227</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
         <v>343</v>
       </c>
       <c r="B32">
         <v>20</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="12" t="s">
         <v>228</v>
       </c>
       <c r="D32" t="s">
@@ -2261,7 +2260,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
         <v>344</v>
       </c>
@@ -2278,7 +2277,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20" t="s">
         <v>345</v>
       </c>
@@ -2295,7 +2294,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
         <v>346</v>
       </c>
@@ -2312,7 +2311,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20"/>
       <c r="B36">
         <v>24</v>
@@ -2327,7 +2326,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20"/>
       <c r="B37">
         <v>25</v>
@@ -2342,7 +2341,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="20"/>
       <c r="B38">
         <v>26</v>
@@ -2357,7 +2356,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="20"/>
       <c r="B39">
         <v>27</v>
@@ -2372,7 +2371,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="20"/>
       <c r="B40">
         <v>28</v>
@@ -2387,7 +2386,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="20"/>
       <c r="B41">
         <v>29</v>
@@ -2402,7 +2401,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="20" t="s">
         <v>347</v>
       </c>
@@ -2419,7 +2418,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="20" t="s">
         <v>348</v>
       </c>
@@ -2436,7 +2435,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="20" t="s">
         <v>349</v>
       </c>
@@ -2453,7 +2452,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="20" t="s">
         <v>350</v>
       </c>
@@ -2470,7 +2469,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20" t="s">
         <v>351</v>
       </c>
@@ -2487,19 +2486,19 @@
         <v>264</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="20"/>
     </row>
-    <row r="48" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="20"/>
       <c r="B48" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="20"/>
     </row>
-    <row r="50" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20"/>
       <c r="B50" t="s">
         <v>177</v>
@@ -2514,7 +2513,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="20" t="s">
         <v>353</v>
       </c>
@@ -2531,7 +2530,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="20" t="s">
         <v>353</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="20" t="s">
         <v>353</v>
       </c>
@@ -2565,7 +2564,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="20" t="s">
         <v>353</v>
       </c>
@@ -2582,7 +2581,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="20" t="s">
         <v>352</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="20" t="s">
         <v>354</v>
       </c>
@@ -2616,7 +2615,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="20" t="s">
         <v>355</v>
       </c>
@@ -2633,7 +2632,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="20" t="s">
         <v>356</v>
       </c>
@@ -2650,7 +2649,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="20" t="s">
         <v>357</v>
       </c>
@@ -2667,7 +2666,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="20" t="s">
         <v>358</v>
       </c>
@@ -2684,7 +2683,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="20" t="s">
         <v>359</v>
       </c>
@@ -2701,7 +2700,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="20" t="s">
         <v>360</v>
       </c>
@@ -2711,14 +2710,14 @@
       <c r="C62" t="s">
         <v>293</v>
       </c>
-      <c r="D62" s="21" t="s">
+      <c r="D62" t="s">
         <v>291</v>
       </c>
       <c r="E62" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="20"/>
       <c r="B63">
         <v>47</v>
@@ -2733,7 +2732,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="20"/>
       <c r="B64">
         <v>48</v>
@@ -2748,7 +2747,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="20"/>
       <c r="B65">
         <v>49</v>
@@ -2763,7 +2762,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="20"/>
       <c r="B66">
         <v>50</v>
@@ -2778,7 +2777,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="20"/>
       <c r="B67">
         <v>51</v>
@@ -2793,7 +2792,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="20" t="s">
         <v>361</v>
       </c>
@@ -2810,7 +2809,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="20" t="s">
         <v>362</v>
       </c>
@@ -2827,7 +2826,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="20"/>
       <c r="B70">
         <v>54</v>
@@ -2842,7 +2841,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="20"/>
       <c r="B71">
         <v>55</v>
@@ -2857,7 +2856,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="20" t="s">
         <v>355</v>
       </c>
@@ -2874,7 +2873,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="20"/>
       <c r="B73">
         <v>57</v>
@@ -2889,7 +2888,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="20"/>
       <c r="B74">
         <v>58</v>
@@ -2904,16 +2903,16 @@
         <v>323</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2922,7 +2921,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F125"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2931,7 +2930,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2951,7 +2950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -2971,7 +2970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -2991,7 +2990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -3011,7 +3010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -3031,7 +3030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -3051,7 +3050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -3071,7 +3070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -3091,7 +3090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -3111,7 +3110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -3131,7 +3130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -3151,7 +3150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -3171,7 +3170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -3191,7 +3190,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -3211,7 +3210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -3231,7 +3230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -3251,7 +3250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -3271,7 +3270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -3291,7 +3290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
@@ -3311,7 +3310,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
@@ -3331,7 +3330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -3351,7 +3350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
@@ -3371,7 +3370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
@@ -3391,7 +3390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
@@ -3411,7 +3410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -3431,7 +3430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
@@ -3451,7 +3450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>24</v>
       </c>
@@ -3471,7 +3470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
@@ -3491,7 +3490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -3511,7 +3510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
@@ -3531,7 +3530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
@@ -3551,7 +3550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>5</v>
       </c>
@@ -3571,7 +3570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -3591,7 +3590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>12</v>
       </c>
@@ -3611,7 +3610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>24</v>
       </c>
@@ -3631,7 +3630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
@@ -3651,7 +3650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>5</v>
       </c>
@@ -3671,7 +3670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>24</v>
       </c>
@@ -3691,7 +3690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>12</v>
       </c>
@@ -3711,7 +3710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>5</v>
       </c>
@@ -3731,7 +3730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>5</v>
       </c>
@@ -3751,7 +3750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>12</v>
       </c>
@@ -3771,7 +3770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>24</v>
       </c>
@@ -3791,7 +3790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>24</v>
       </c>
@@ -3811,7 +3810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -3831,7 +3830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>5</v>
       </c>
@@ -3851,7 +3850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>24</v>
       </c>
@@ -3871,7 +3870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>5</v>
       </c>
@@ -3891,7 +3890,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>5</v>
       </c>
@@ -3911,7 +3910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>24</v>
       </c>
@@ -3931,7 +3930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>24</v>
       </c>
@@ -3951,7 +3950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
@@ -3971,7 +3970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>12</v>
       </c>
@@ -3991,7 +3990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>24</v>
       </c>
@@ -4011,7 +4010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>12</v>
       </c>
@@ -4031,7 +4030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -4051,7 +4050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -4071,7 +4070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>24</v>
       </c>
@@ -4091,7 +4090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>24</v>
       </c>
@@ -4111,7 +4110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>24</v>
       </c>
@@ -4131,7 +4130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>24</v>
       </c>
@@ -4151,7 +4150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>5</v>
       </c>
@@ -4171,7 +4170,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>24</v>
       </c>
@@ -4191,7 +4190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>24</v>
       </c>
@@ -4211,7 +4210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>24</v>
       </c>
@@ -4231,7 +4230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>24</v>
       </c>
@@ -4251,7 +4250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>12</v>
       </c>
@@ -4271,7 +4270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>24</v>
       </c>
@@ -4291,7 +4290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>24</v>
       </c>
@@ -4311,7 +4310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>24</v>
       </c>
@@ -4331,7 +4330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>12</v>
       </c>
@@ -4351,7 +4350,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>24</v>
       </c>
@@ -4371,7 +4370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -4391,7 +4390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>12</v>
       </c>
@@ -4411,7 +4410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>24</v>
       </c>
@@ -4431,7 +4430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>5</v>
       </c>
@@ -4451,7 +4450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>24</v>
       </c>
@@ -4471,7 +4470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>24</v>
       </c>
@@ -4491,7 +4490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>5</v>
       </c>
@@ -4511,7 +4510,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>24</v>
       </c>
@@ -4531,7 +4530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>24</v>
       </c>
@@ -4551,7 +4550,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>12</v>
       </c>
@@ -4571,7 +4570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>24</v>
       </c>
@@ -4591,7 +4590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>24</v>
       </c>
@@ -4611,7 +4610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>24</v>
       </c>
@@ -4631,7 +4630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>12</v>
       </c>
@@ -4651,7 +4650,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>5</v>
       </c>
@@ -4671,7 +4670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>24</v>
       </c>
@@ -4691,7 +4690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>12</v>
       </c>
@@ -4711,7 +4710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>24</v>
       </c>
@@ -4731,7 +4730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>12</v>
       </c>
@@ -4751,7 +4750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>24</v>
       </c>
@@ -4771,7 +4770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>24</v>
       </c>
@@ -4791,7 +4790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>24</v>
       </c>
@@ -4811,7 +4810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>24</v>
       </c>
@@ -4831,7 +4830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>24</v>
       </c>
@@ -4851,7 +4850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>24</v>
       </c>
@@ -4871,7 +4870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>5</v>
       </c>
@@ -4891,7 +4890,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>24</v>
       </c>
@@ -4911,7 +4910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>24</v>
       </c>
@@ -4931,7 +4930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>24</v>
       </c>
@@ -4951,7 +4950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>24</v>
       </c>
@@ -4971,7 +4970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>5</v>
       </c>
@@ -4985,7 +4984,7 @@
       <c r="E103" s="5"/>
       <c r="F103" s="6"/>
     </row>
-    <row r="104" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>5</v>
       </c>
@@ -4999,7 +4998,7 @@
       <c r="E104" s="5"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>5</v>
       </c>
@@ -5013,7 +5012,7 @@
       <c r="E105" s="5"/>
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>5</v>
       </c>
@@ -5027,7 +5026,7 @@
       <c r="E106" s="16"/>
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>5</v>
       </c>
@@ -5041,7 +5040,7 @@
       <c r="E107" s="16"/>
       <c r="F107" s="6"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>12</v>
       </c>
@@ -5055,7 +5054,7 @@
       <c r="E108" s="5"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>12</v>
       </c>
@@ -5069,7 +5068,7 @@
       <c r="E109" s="5"/>
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>12</v>
       </c>
@@ -5083,7 +5082,7 @@
       <c r="E110" s="5"/>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>12</v>
       </c>
@@ -5097,7 +5096,7 @@
       <c r="E111" s="5"/>
       <c r="F111" s="6"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>12</v>
       </c>
@@ -5111,7 +5110,7 @@
       <c r="E112" s="5"/>
       <c r="F112" s="6"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>24</v>
       </c>
@@ -5125,7 +5124,7 @@
       <c r="E113" s="5"/>
       <c r="F113" s="6"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>24</v>
       </c>
@@ -5139,7 +5138,7 @@
       <c r="E114" s="5"/>
       <c r="F114" s="6"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>24</v>
       </c>
@@ -5153,7 +5152,7 @@
       <c r="E115" s="5"/>
       <c r="F115" s="6"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>24</v>
       </c>
@@ -5167,7 +5166,7 @@
       <c r="E116" s="5"/>
       <c r="F116" s="6"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>24</v>
       </c>
@@ -5181,7 +5180,7 @@
       <c r="E117" s="5"/>
       <c r="F117" s="6"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>24</v>
       </c>
@@ -5195,7 +5194,7 @@
       <c r="E118" s="5"/>
       <c r="F118" s="6"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>24</v>
       </c>
@@ -5209,7 +5208,7 @@
       <c r="E119" s="5"/>
       <c r="F119" s="6"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>24</v>
       </c>
@@ -5223,7 +5222,7 @@
       <c r="E120" s="5"/>
       <c r="F120" s="6"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>24</v>
       </c>
@@ -5237,7 +5236,7 @@
       <c r="E121" s="5"/>
       <c r="F121" s="6"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>24</v>
       </c>
@@ -5251,7 +5250,7 @@
       <c r="E122" s="5"/>
       <c r="F122" s="6"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>24</v>
       </c>
@@ -5265,7 +5264,7 @@
       <c r="E123" s="5"/>
       <c r="F123" s="6"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="10" t="s">
         <v>24</v>
       </c>
@@ -5277,7 +5276,7 @@
       </c>
       <c r="F124" s="6"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F125" s="19"/>
     </row>
   </sheetData>
@@ -5293,7 +5292,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -5302,7 +5301,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5322,7 +5321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -5351,7 +5350,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -5360,7 +5359,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5380,7 +5379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -5400,7 +5399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -5420,7 +5419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -5440,7 +5439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -5460,7 +5459,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -5480,7 +5479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -5494,7 +5493,7 @@
       <c r="E7" s="5"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -5514,7 +5513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -5528,7 +5527,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -5548,7 +5547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
@@ -5568,7 +5567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -5582,7 +5581,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -5602,7 +5601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -5622,7 +5621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -5642,7 +5641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
@@ -5662,7 +5661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
@@ -5682,7 +5681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -5702,7 +5701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
@@ -5722,7 +5721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
@@ -5742,7 +5741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>5</v>
       </c>
@@ -5762,7 +5761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
@@ -5773,7 +5772,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>5</v>
       </c>
@@ -5793,7 +5792,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -5802,7 +5801,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5822,7 +5821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -5842,7 +5841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -5862,7 +5861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -5882,7 +5881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -5896,7 +5895,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -5916,7 +5915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -5936,7 +5935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -5956,7 +5955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -5976,7 +5975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -5996,7 +5995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -6010,7 +6009,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -6024,7 +6023,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -6038,7 +6037,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -6058,7 +6057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -6078,7 +6077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
@@ -6098,7 +6097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -6118,7 +6117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>12</v>
       </c>
@@ -6138,7 +6137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
@@ -6158,7 +6157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
@@ -6178,7 +6177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -6198,7 +6197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>12</v>
       </c>
@@ -6218,7 +6217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>12</v>
       </c>
@@ -6232,7 +6231,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
@@ -6252,7 +6251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -6272,7 +6271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
@@ -6292,7 +6291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>12</v>
       </c>
@@ -6312,7 +6311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>12</v>
       </c>
@@ -6332,7 +6331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -6352,7 +6351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>12</v>
       </c>
@@ -6372,7 +6371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
@@ -6392,7 +6391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
@@ -6412,7 +6411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -6432,7 +6431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>12</v>
       </c>
@@ -6452,7 +6451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
@@ -6472,7 +6471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
@@ -6492,7 +6491,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>12</v>
       </c>
@@ -6521,7 +6520,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -6530,7 +6529,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6550,7 +6549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -6579,7 +6578,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -6588,7 +6587,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6608,7 +6607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -6628,7 +6627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -6642,7 +6641,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -6662,7 +6661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -6676,7 +6675,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -6696,7 +6695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -6716,7 +6715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -6736,7 +6735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -6756,7 +6755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -6776,7 +6775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -6796,7 +6795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -6816,7 +6815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -6836,7 +6835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -6856,7 +6855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -6876,7 +6875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -6896,7 +6895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -6916,7 +6915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -6930,7 +6929,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
@@ -6944,7 +6943,7 @@
       <c r="E19" s="5"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
@@ -6958,7 +6957,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
@@ -6978,7 +6977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
@@ -6998,7 +6997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
@@ -7018,7 +7017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
@@ -7038,7 +7037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -7058,7 +7057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
@@ -7078,7 +7077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>24</v>
       </c>
@@ -7098,7 +7097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
@@ -7118,7 +7117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
@@ -7138,7 +7137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
@@ -7158,7 +7157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>24</v>
       </c>
@@ -7178,7 +7177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>24</v>
       </c>
@@ -7192,7 +7191,7 @@
       <c r="E32" s="5"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>24</v>
       </c>
@@ -7212,7 +7211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>24</v>
       </c>
@@ -7226,7 +7225,7 @@
       <c r="E34" s="5"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>24</v>
       </c>
@@ -7240,7 +7239,7 @@
       <c r="E35" s="5"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>24</v>
       </c>
@@ -7260,7 +7259,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>24</v>
       </c>
@@ -7280,7 +7279,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>24</v>
       </c>
@@ -7300,7 +7299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>24</v>
       </c>
@@ -7320,7 +7319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>24</v>
       </c>
@@ -7340,7 +7339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>24</v>
       </c>
@@ -7360,7 +7359,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>24</v>
       </c>
@@ -7380,7 +7379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>24</v>
       </c>
@@ -7400,7 +7399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>24</v>
       </c>
@@ -7420,7 +7419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>24</v>
       </c>
@@ -7434,7 +7433,7 @@
       <c r="E45" s="5"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>24</v>
       </c>
@@ -7448,7 +7447,7 @@
       <c r="E46" s="5"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>24</v>
       </c>
@@ -7468,7 +7467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>24</v>
       </c>
@@ -7488,7 +7487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>24</v>
       </c>
@@ -7508,7 +7507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>24</v>
       </c>
@@ -7528,7 +7527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>24</v>
       </c>
@@ -7548,7 +7547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>24</v>
       </c>
@@ -7568,7 +7567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>24</v>
       </c>
@@ -7588,7 +7587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>24</v>
       </c>
@@ -7602,7 +7601,7 @@
       <c r="E54" s="5"/>
       <c r="F54" s="6"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>24</v>
       </c>
@@ -7622,7 +7621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>24</v>
       </c>
@@ -7642,7 +7641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>24</v>
       </c>
@@ -7662,7 +7661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>24</v>
       </c>
@@ -7682,7 +7681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>24</v>
       </c>
@@ -7702,7 +7701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>24</v>
       </c>
@@ -7722,7 +7721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>24</v>
       </c>
@@ -7742,7 +7741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>24</v>
       </c>
@@ -7762,7 +7761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>24</v>
       </c>
@@ -7782,7 +7781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>24</v>
       </c>
@@ -7802,7 +7801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>24</v>
       </c>
@@ -7822,7 +7821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>24</v>
       </c>
@@ -7842,7 +7841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>24</v>
       </c>
@@ -7862,7 +7861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>24</v>
       </c>
@@ -7882,7 +7881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>24</v>
       </c>
@@ -7902,7 +7901,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
         <v>24</v>
       </c>

--- a/OUT_25-26_M2_BM_universites.xlsx
+++ b/OUT_25-26_M2_BM_universites.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coulono\Downloads\Navigo - perso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F76A9D-A721-487A-AC4F-574BC52987BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A93676-A98C-4FD9-9839-6D491C52A8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13785" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="8" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="372">
   <si>
     <t>Continent</t>
   </si>
@@ -1146,6 +1146,59 @@
   </si>
   <si>
     <t xml:space="preserve">Tier 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pas les notes du tout </t>
+  </si>
+  <si>
+    <t>pas de bon programme du tout : Accounting
+Business Environment and Policy
+Strategic Business Valuation
+Human Resources &amp; Management
+Management Information Systems
+Strategic Marketing
+Operations Management
+Health Services Management</t>
+  </si>
+  <si>
+    <t>cours de merde : 8103 - Statistical Applications in Management
+8104 - Organizations: Behaviour and Structure
+8106 - Marketing
+8108 - Economics for Business
+8109 - Accounting for Management
+8204 - Human Resources Management
+8205 - Information Systems
+8206 - Managerial Finance
+8207 - Operations Management
+8208 - Strategic Management</t>
+  </si>
+  <si>
+    <t>que des cours de merde (accounting, management, sustainability…) quelques cours de data mais y en a que 2 qui valent rien (2 qui valent 3 crédits respectivement)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+One-Year MBA Program Overview
+One Year. Maximum Impact.
+In today’s competitive landscape, the best investment is one that delivers immediate results. Our one-year MBA is a high-impact launchpad for the next generation of business leaders.
+Focused entirely on real-world application, the University of Alberta MBA equips you with the tools to solve complex challenges in real-time. Through dedicated career coaching and an intensive capstone experience, you will emerge ready to achieve your career goals with a degree that works as hard as you do. 
+You also have the opportunity to pursue your MBA alongside other programs through our formal combined degrees.  
+Program Outline
+In just one year, you’ll master the essentials of management across eight core courses. You’ll broaden your outlook with an international course and bring it all together by tackling a real-world project in your capstone. To make the degree your own, you can choose four electives that align with your passions, graduating with a toolkit built for where you want to go next. Explore the Full-Time MBA Outline.
+Orientation
+Your MBA journey begins in August with a week designed to launch your career from day one. Orientation is more than just an introduction — it’s a deep dive into self-reflection and team building. You’ll connect with your cohort to build a professional community that supports you through this intensive year and follows you throughout your career. Start your degree with a clear vision and a network that lasts a lifetime
+Core Curriculum
+The foundation of the MBA program, through the core courses you'll develop and strengthen your business knowledge.  
+ACCTG 501: Accounting for Managers
+BUAN 501: Data Analysis and Decision Making
+BUEC 501: Economics for Managers
+BUS 505: Leadership &amp; Society
+FIN 501: Managerial Finance
+MARK 501: Marketing Management
+SEM 501: Leading People
+SEM 502: Organizational Strategy</t>
+  </si>
+  <si>
+    <t>un cours de fintech qui peut être pas mal, mais le reste est bien à chier (refaire FSA : jamais par pitié)</t>
   </si>
 </sst>
 </file>
@@ -1312,16 +1365,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1335,6 +1379,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1639,189 +1692,189 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8D01D8-A348-4A3C-A33B-1505E738259C}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="141.6640625" customWidth="1"/>
+    <col min="1" max="1" width="39.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="141.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
         <v>363</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="24" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="B2" s="28" t="str">
+      <c r="B2" s="25" t="str">
         <f>_xlfn.XLOOKUP(A2,Tierlist!C:C,Tierlist!A:A)</f>
         <v>Maitreclasse</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="25" t="str">
         <f>_xlfn.XLOOKUP(A3,Tierlist!C:C,Tierlist!A:A)</f>
         <v>semble plutôt banger ça, beaucoup de cours quantitatifs, visiblement pas de limite sur ce qu'on peut prendre</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="28" t="str">
+      <c r="B4" s="25" t="str">
         <f>_xlfn.XLOOKUP(A4,Tierlist!C:C,Tierlist!A:A)</f>
         <v>cours vraiment bien (à la fois quantitatif, mais aussi bcp de data), à voir acceptation edhec ("it is not possible to specialize in Economics during this exchange and Finance courses are generally not accepted for credit transfer except courses related to the fields of Accounting and Auditing")</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="28" t="str">
+      <c r="B5" s="25" t="str">
         <f>_xlfn.XLOOKUP(A5,Tierlist!C:C,Tierlist!A:A)</f>
         <v>choix de cours plutôt large et bien adapté, top cours : Asset management, Money, banking &amp; financial markets, time series analysis &amp; machine learning</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="B6" s="28" t="str">
+      <c r="B6" s="25" t="str">
         <f>_xlfn.XLOOKUP(A6,Tierlist!C:C,Tierlist!A:A)</f>
         <v>vraiment bon choix, cours pertinents : Derivatives, neural networks for Eco and Finance, advanced monetary policy, macroeconometrics, time series analysis,asset pricing, financial econometrics</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="B7" s="28" t="str">
+      <c r="B7" s="25" t="str">
         <f>_xlfn.XLOOKUP(A7,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">Big, cours vraiment pertinents, à voir éligibilité edhec </v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="B8" s="28" t="str">
+      <c r="B8" s="25" t="str">
         <f>_xlfn.XLOOKUP(A8,Tierlist!C:C,Tierlist!A:A)</f>
         <v>Cours vraiment bien sur campus bruxelles (est ce que je veux aller dans cacaville Bruxelles : non)</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="B9" s="28" t="str">
+      <c r="B9" s="25" t="str">
         <f>_xlfn.XLOOKUP(A9,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">derivatives dispo : maitreclassique </v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="B10" s="28" t="str">
+      <c r="B10" s="25" t="str">
         <f>_xlfn.XLOOKUP(A10,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">idem que WHU koblenz : mid mais reste ok </v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="B11" s="28" t="str">
+      <c r="B11" s="25" t="str">
         <f>_xlfn.XLOOKUP(A11,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">chine, sinon pas de bon programme </v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B12" s="20"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="17"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="25" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="B14" s="28" t="str">
+      <c r="B14" s="25" t="str">
         <f>_xlfn.XLOOKUP(A14,Tierlist!C:C,Tierlist!A:A)</f>
         <v>échange cool, cours absolument réduits a néant a cause edhec</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="B15" s="28" t="str">
+      <c r="B15" s="25" t="str">
         <f>_xlfn.XLOOKUP(A15,Tierlist!C:C,Tierlist!A:A)</f>
         <v>2 cours intéressants, le reste pue</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="28" t="str">
+      <c r="B16" s="25" t="str">
         <f>_xlfn.XLOOKUP(A16,Tierlist!C:C,Tierlist!A:A)</f>
         <v>programmes pas trop clairs car sont présentés en 2ans, mais programme Msc economic and finance - Advanced eco and finance plutôt pas mal au global</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="28" t="str">
+      <c r="B17" s="25" t="str">
         <f>_xlfn.XLOOKUP(A17,Tierlist!C:C,Tierlist!A:A)</f>
         <v>idem, cours interessants mais pascompris ce qu'on avait le droit de prendre</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="B18" s="28" t="str">
+      <c r="B18" s="25" t="str">
         <f>_xlfn.XLOOKUP(A18,Tierlist!C:C,Tierlist!A:A)</f>
         <v>pas de derivatives, pas d'asset pricing, mais cours quantitatifs quand même</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="B19" s="28" t="str">
+      <c r="B19" s="25" t="str">
         <f>_xlfn.XLOOKUP(A19,Tierlist!C:C,Tierlist!A:A)</f>
         <v>rien pané au choix des cours, mais y a des très bons cours quantitatifs</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="B20" s="28" t="str">
+      <c r="B20" s="25" t="str">
         <f>_xlfn.XLOOKUP(A20,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">MSc in Information Science and Technology Management why not, sinon pas ed choses pour front </v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="B21" s="28" t="str">
+      <c r="B21" s="25" t="str">
         <f>_xlfn.XLOOKUP(A21,Tierlist!C:C,Tierlist!A:A)</f>
         <v xml:space="preserve">chine, sinon pas de bon programme </v>
       </c>
@@ -1834,16 +1887,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E84"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="74.77734375" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="55.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="81.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="74.7265625" customWidth="1"/>
+    <col min="2" max="2" width="6.36328125" customWidth="1"/>
+    <col min="3" max="3" width="55.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="81.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>324</v>
       </c>
@@ -1851,8 +1904,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>177</v>
       </c>
@@ -1866,8 +1919,8 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
         <v>325</v>
       </c>
       <c r="B5">
@@ -1883,8 +1936,8 @@
         <v>182</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
         <v>326</v>
       </c>
       <c r="B6">
@@ -1900,8 +1953,8 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
         <v>331</v>
       </c>
       <c r="B7">
@@ -1917,8 +1970,8 @@
         <v>188</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
         <v>329</v>
       </c>
       <c r="B8">
@@ -1934,8 +1987,8 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
         <v>328</v>
       </c>
       <c r="B9">
@@ -1951,20 +2004,20 @@
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
-    </row>
-    <row r="11" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="20"/>
+    <row r="10" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17"/>
+    </row>
+    <row r="11" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17"/>
       <c r="B11" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
-    </row>
-    <row r="13" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
+    <row r="12" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17"/>
+    </row>
+    <row r="13" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17"/>
       <c r="B13" t="s">
         <v>177</v>
       </c>
@@ -1978,8 +2031,8 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+    <row r="14" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
         <v>330</v>
       </c>
       <c r="B14">
@@ -1995,8 +2048,8 @@
         <v>196</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+    <row r="15" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
         <v>327</v>
       </c>
       <c r="B15">
@@ -2012,14 +2065,14 @@
         <v>198</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
+    <row r="16" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
         <v>332</v>
       </c>
       <c r="B16">
         <v>8</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="13" t="s">
         <v>199</v>
       </c>
       <c r="D16" t="s">
@@ -2029,8 +2082,8 @@
         <v>201</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
+    <row r="17" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
         <v>333</v>
       </c>
       <c r="B17">
@@ -2046,8 +2099,8 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
+    <row r="18" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
         <v>325</v>
       </c>
       <c r="B18">
@@ -2063,8 +2116,8 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
+    <row r="19" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
         <v>334</v>
       </c>
       <c r="B19">
@@ -2080,8 +2133,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
+    <row r="20" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
         <v>335</v>
       </c>
       <c r="B20">
@@ -2097,8 +2150,8 @@
         <v>210</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
+    <row r="21" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17" t="s">
         <v>336</v>
       </c>
       <c r="B21">
@@ -2114,8 +2167,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
+    <row r="22" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="17" t="s">
         <v>337</v>
       </c>
       <c r="B22">
@@ -2131,8 +2184,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+    <row r="23" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="17" t="s">
         <v>338</v>
       </c>
       <c r="B23">
@@ -2148,8 +2201,8 @@
         <v>217</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="17" t="s">
         <v>339</v>
       </c>
       <c r="B24">
@@ -2165,20 +2218,20 @@
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="20"/>
-    </row>
-    <row r="26" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="20"/>
+    <row r="25" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="17"/>
+    </row>
+    <row r="26" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="17"/>
       <c r="B26" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="20"/>
-    </row>
-    <row r="28" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="20"/>
+    <row r="27" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="17"/>
+    </row>
+    <row r="28" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="17"/>
       <c r="B28" t="s">
         <v>177</v>
       </c>
@@ -2192,8 +2245,8 @@
         <v>179</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="s">
+    <row r="29" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="17" t="s">
         <v>340</v>
       </c>
       <c r="B29">
@@ -2209,8 +2262,8 @@
         <v>223</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="20" t="s">
+    <row r="30" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="17" t="s">
         <v>341</v>
       </c>
       <c r="B30">
@@ -2226,8 +2279,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="20" t="s">
+    <row r="31" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="17" t="s">
         <v>342</v>
       </c>
       <c r="B31">
@@ -2243,14 +2296,14 @@
         <v>227</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="s">
+    <row r="32" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="17" t="s">
         <v>343</v>
       </c>
       <c r="B32">
         <v>20</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="14" t="s">
         <v>228</v>
       </c>
       <c r="D32" t="s">
@@ -2260,8 +2313,8 @@
         <v>230</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
+    <row r="33" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="17" t="s">
         <v>344</v>
       </c>
       <c r="B33">
@@ -2277,8 +2330,8 @@
         <v>232</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="20" t="s">
+    <row r="34" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="17" t="s">
         <v>345</v>
       </c>
       <c r="B34">
@@ -2294,8 +2347,8 @@
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
+    <row r="35" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="17" t="s">
         <v>346</v>
       </c>
       <c r="B35">
@@ -2311,8 +2364,8 @@
         <v>237</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="20"/>
+    <row r="36" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="17"/>
       <c r="B36">
         <v>24</v>
       </c>
@@ -2326,8 +2379,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="20"/>
+    <row r="37" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="17"/>
       <c r="B37">
         <v>25</v>
       </c>
@@ -2341,8 +2394,8 @@
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="20"/>
+    <row r="38" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="17"/>
       <c r="B38">
         <v>26</v>
       </c>
@@ -2356,8 +2409,8 @@
         <v>244</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="20"/>
+    <row r="39" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="17"/>
       <c r="B39">
         <v>27</v>
       </c>
@@ -2371,8 +2424,8 @@
         <v>246</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="20"/>
+    <row r="40" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="17"/>
       <c r="B40">
         <v>28</v>
       </c>
@@ -2386,8 +2439,8 @@
         <v>249</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="20"/>
+    <row r="41" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="17"/>
       <c r="B41">
         <v>29</v>
       </c>
@@ -2401,8 +2454,8 @@
         <v>251</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="20" t="s">
+    <row r="42" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="17" t="s">
         <v>347</v>
       </c>
       <c r="B42">
@@ -2418,8 +2471,8 @@
         <v>254</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="20" t="s">
+    <row r="43" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="17" t="s">
         <v>348</v>
       </c>
       <c r="B43">
@@ -2435,8 +2488,8 @@
         <v>257</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="20" t="s">
+    <row r="44" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="17" t="s">
         <v>349</v>
       </c>
       <c r="B44">
@@ -2452,8 +2505,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="20" t="s">
+    <row r="45" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="17" t="s">
         <v>350</v>
       </c>
       <c r="B45">
@@ -2469,8 +2522,8 @@
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="20" t="s">
+    <row r="46" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="17" t="s">
         <v>351</v>
       </c>
       <c r="B46">
@@ -2486,20 +2539,20 @@
         <v>264</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
-    </row>
-    <row r="48" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="20"/>
+    <row r="47" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="17"/>
+    </row>
+    <row r="48" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="17"/>
       <c r="B48" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="20"/>
-    </row>
-    <row r="50" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="20"/>
+    <row r="49" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="17"/>
+    </row>
+    <row r="50" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="17"/>
       <c r="B50" t="s">
         <v>177</v>
       </c>
@@ -2513,8 +2566,8 @@
         <v>179</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="20" t="s">
+    <row r="51" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="17" t="s">
         <v>353</v>
       </c>
       <c r="B51">
@@ -2530,8 +2583,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="20" t="s">
+    <row r="52" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="17" t="s">
         <v>353</v>
       </c>
       <c r="B52">
@@ -2547,8 +2600,8 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="20" t="s">
+    <row r="53" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="17" t="s">
         <v>353</v>
       </c>
       <c r="B53">
@@ -2564,8 +2617,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="20" t="s">
+    <row r="54" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="17" t="s">
         <v>353</v>
       </c>
       <c r="B54">
@@ -2581,8 +2634,8 @@
         <v>275</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="20" t="s">
+    <row r="55" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="17" t="s">
         <v>352</v>
       </c>
       <c r="B55">
@@ -2598,8 +2651,8 @@
         <v>277</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="20" t="s">
+    <row r="56" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="17" t="s">
         <v>354</v>
       </c>
       <c r="B56">
@@ -2615,8 +2668,8 @@
         <v>280</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="20" t="s">
+    <row r="57" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="17" t="s">
         <v>355</v>
       </c>
       <c r="B57">
@@ -2632,8 +2685,8 @@
         <v>282</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="20" t="s">
+    <row r="58" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="17" t="s">
         <v>356</v>
       </c>
       <c r="B58">
@@ -2649,8 +2702,8 @@
         <v>284</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="20" t="s">
+    <row r="59" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="17" t="s">
         <v>357</v>
       </c>
       <c r="B59">
@@ -2666,8 +2719,8 @@
         <v>286</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="20" t="s">
+    <row r="60" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="17" t="s">
         <v>358</v>
       </c>
       <c r="B60">
@@ -2683,8 +2736,8 @@
         <v>289</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="20" t="s">
+    <row r="61" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="17" t="s">
         <v>359</v>
       </c>
       <c r="B61">
@@ -2700,8 +2753,8 @@
         <v>292</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="20" t="s">
+    <row r="62" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="17" t="s">
         <v>360</v>
       </c>
       <c r="B62">
@@ -2717,8 +2770,8 @@
         <v>294</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="20"/>
+    <row r="63" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="17"/>
       <c r="B63">
         <v>47</v>
       </c>
@@ -2732,8 +2785,8 @@
         <v>297</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="20"/>
+    <row r="64" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="17"/>
       <c r="B64">
         <v>48</v>
       </c>
@@ -2747,8 +2800,8 @@
         <v>299</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="20"/>
+    <row r="65" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="17"/>
       <c r="B65">
         <v>49</v>
       </c>
@@ -2762,8 +2815,8 @@
         <v>301</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="20"/>
+    <row r="66" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="17"/>
       <c r="B66">
         <v>50</v>
       </c>
@@ -2777,8 +2830,8 @@
         <v>303</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="20"/>
+    <row r="67" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="17"/>
       <c r="B67">
         <v>51</v>
       </c>
@@ -2792,8 +2845,8 @@
         <v>305</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="20" t="s">
+    <row r="68" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="17" t="s">
         <v>361</v>
       </c>
       <c r="B68">
@@ -2809,8 +2862,8 @@
         <v>308</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="20" t="s">
+    <row r="69" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="17" t="s">
         <v>362</v>
       </c>
       <c r="B69">
@@ -2826,8 +2879,8 @@
         <v>311</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="20"/>
+    <row r="70" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="17"/>
       <c r="B70">
         <v>54</v>
       </c>
@@ -2841,8 +2894,8 @@
         <v>313</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="20"/>
+    <row r="71" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="17"/>
       <c r="B71">
         <v>55</v>
       </c>
@@ -2856,8 +2909,8 @@
         <v>316</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="20" t="s">
+    <row r="72" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="17" t="s">
         <v>355</v>
       </c>
       <c r="B72">
@@ -2873,8 +2926,8 @@
         <v>318</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="20"/>
+    <row r="73" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="17"/>
       <c r="B73">
         <v>57</v>
       </c>
@@ -2888,8 +2941,8 @@
         <v>321</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="20"/>
+    <row r="74" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="17"/>
       <c r="B74">
         <v>58</v>
       </c>
@@ -2903,16 +2956,16 @@
         <v>323</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" spans="1:5" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="21.45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="21.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2921,16 +2974,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F125"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="77" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2950,2027 +3004,2027 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D2" s="5">
-        <v>15.67</v>
+        <v>11.27</v>
       </c>
       <c r="E2" s="5">
-        <v>16.6175</v>
+        <v>12.86</v>
       </c>
       <c r="F2" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="D3" s="5">
-        <v>15.6</v>
+        <v>11.425000000000001</v>
       </c>
       <c r="E3" s="5">
-        <v>15.6</v>
+        <v>11.425000000000001</v>
       </c>
       <c r="F3" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="5">
+        <v>11.85</v>
+      </c>
+      <c r="E4" s="5">
+        <v>12.574999999999999</v>
+      </c>
+      <c r="F4" s="6">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="5">
+        <v>11.855</v>
+      </c>
+      <c r="E5" s="5">
+        <v>13.13</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="5">
-        <v>15.51</v>
-      </c>
-      <c r="E4" s="5">
-        <v>15.51</v>
-      </c>
-      <c r="F4" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="5">
-        <v>15.44</v>
-      </c>
-      <c r="E5" s="5">
-        <v>15.44</v>
-      </c>
-      <c r="F5" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="C6" s="7" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="D6" s="5">
-        <v>15.21</v>
+        <v>11.96</v>
       </c>
       <c r="E6" s="5">
-        <v>16.872499999999999</v>
+        <v>12.76</v>
       </c>
       <c r="F6" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="D7" s="5">
-        <v>15.05</v>
+        <v>12.035</v>
       </c>
       <c r="E7" s="5">
-        <v>15.545</v>
+        <v>12.08</v>
       </c>
       <c r="F7" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="D8" s="5">
-        <v>15.04</v>
+        <v>12.135</v>
       </c>
       <c r="E8" s="5">
-        <v>15.04</v>
+        <v>12.35</v>
       </c>
       <c r="F8" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="5">
+        <v>12.25</v>
+      </c>
+      <c r="E9" s="5">
+        <v>12.36</v>
+      </c>
+      <c r="F9" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="5">
+        <v>12.265000000000001</v>
+      </c>
+      <c r="E10" s="5">
+        <v>13.12</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="5">
+        <v>12.32</v>
+      </c>
+      <c r="E11" s="5">
+        <v>12.33</v>
+      </c>
+      <c r="F11" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="5">
+        <v>12.34</v>
+      </c>
+      <c r="E12" s="5">
+        <v>12.34</v>
+      </c>
+      <c r="F12" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="5">
-        <v>15.02</v>
-      </c>
-      <c r="E9" s="5">
-        <v>15.02</v>
-      </c>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="5">
-        <v>15.005000000000001</v>
-      </c>
-      <c r="E10" s="5">
-        <v>15.005000000000001</v>
-      </c>
-      <c r="F10" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="5">
-        <v>14.9</v>
-      </c>
-      <c r="E11" s="5">
-        <v>14.9</v>
-      </c>
-      <c r="F11" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="5">
-        <v>14.85</v>
-      </c>
-      <c r="E12" s="5">
-        <v>14.9</v>
-      </c>
-      <c r="F12" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D13" s="5">
-        <v>14.785</v>
+        <v>12.37</v>
       </c>
       <c r="E13" s="5">
-        <v>15.15</v>
+        <v>12.37</v>
       </c>
       <c r="F13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="5">
+        <v>12.395</v>
+      </c>
+      <c r="E14" s="5">
+        <v>12.82</v>
+      </c>
+      <c r="F14" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="5">
-        <v>14.78</v>
-      </c>
-      <c r="E14" s="5">
-        <v>14.78</v>
-      </c>
-      <c r="F14" s="6">
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="5">
+        <v>12.42</v>
+      </c>
+      <c r="E15" s="5">
+        <v>13.33</v>
+      </c>
+      <c r="F15" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" s="5">
+        <v>12.44</v>
+      </c>
+      <c r="E16" s="5">
+        <v>13.43</v>
+      </c>
+      <c r="F16" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="5">
+        <v>12.45</v>
+      </c>
+      <c r="E17" s="5">
+        <v>14.32</v>
+      </c>
+      <c r="F17" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="5">
+        <v>12.48</v>
+      </c>
+      <c r="E18" s="5">
+        <v>15.08</v>
+      </c>
+      <c r="F18" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="5">
+        <v>12.484999999999999</v>
+      </c>
+      <c r="E19" s="5">
+        <v>12.484999999999999</v>
+      </c>
+      <c r="F19" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" s="5">
-        <v>14.63</v>
-      </c>
-      <c r="E15" s="5">
-        <v>14.8225</v>
-      </c>
-      <c r="F15" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D16" s="5">
-        <v>14.63</v>
-      </c>
-      <c r="E16" s="5">
-        <v>14.63</v>
-      </c>
-      <c r="F16" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D17" s="5">
-        <v>14.63</v>
-      </c>
-      <c r="E17" s="5">
-        <v>14.63</v>
-      </c>
-      <c r="F17" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="5">
-        <v>14.54</v>
-      </c>
-      <c r="E18" s="5">
-        <v>14.54</v>
-      </c>
-      <c r="F18" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="5">
-        <v>14.52</v>
-      </c>
-      <c r="E19" s="5">
-        <v>15.57</v>
-      </c>
-      <c r="F19" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="D20" s="5">
-        <v>14.39</v>
+        <v>12.52</v>
       </c>
       <c r="E20" s="5">
-        <v>14.4</v>
+        <v>12.75</v>
       </c>
       <c r="F20" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="D21" s="5">
-        <v>14.39</v>
+        <v>12.525</v>
       </c>
       <c r="E21" s="5">
-        <v>14.39</v>
+        <v>12.525</v>
       </c>
       <c r="F21" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" s="17">
-        <v>14.21</v>
-      </c>
-      <c r="E22" s="17">
-        <v>15.654999999999999</v>
-      </c>
-      <c r="F22" s="18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="27">
+        <v>12.54</v>
+      </c>
+      <c r="E22" s="27">
+        <v>13.05</v>
+      </c>
+      <c r="F22" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" s="17">
-        <v>14.11</v>
-      </c>
-      <c r="E23" s="17">
-        <v>15.08</v>
-      </c>
-      <c r="F23" s="18">
+        <v>34</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="27">
+        <v>12.55</v>
+      </c>
+      <c r="E23" s="27">
+        <v>13.68</v>
+      </c>
+      <c r="F23" s="28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="5">
+        <v>12.57</v>
+      </c>
+      <c r="E24" s="5">
+        <v>13.52</v>
+      </c>
+      <c r="F24" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="5">
-        <v>14.085000000000001</v>
-      </c>
-      <c r="E24" s="5">
-        <v>14.73</v>
-      </c>
-      <c r="F24" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D25" s="5">
-        <v>14.06</v>
+        <v>12.57</v>
       </c>
       <c r="E25" s="5">
-        <v>14.1</v>
+        <v>12.57</v>
       </c>
       <c r="F25" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="D26" s="5">
-        <v>14.045</v>
+        <v>12.615</v>
       </c>
       <c r="E26" s="5">
-        <v>15.35</v>
+        <v>13.17</v>
       </c>
       <c r="F26" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D27" s="5">
-        <v>14.01</v>
+        <v>12.66</v>
       </c>
       <c r="E27" s="5">
-        <v>15.32</v>
+        <v>13.095000000000001</v>
       </c>
       <c r="F27" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="D28" s="5">
-        <v>13.994999999999999</v>
+        <v>12.72</v>
       </c>
       <c r="E28" s="5">
-        <v>14.4</v>
+        <v>14.27</v>
       </c>
       <c r="F28" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D29" s="5">
-        <v>13.975</v>
+        <v>12.74</v>
       </c>
       <c r="E29" s="5">
-        <v>14.38</v>
+        <v>13.37</v>
       </c>
       <c r="F29" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="D30" s="5">
-        <v>13.945</v>
+        <v>12.74</v>
       </c>
       <c r="E30" s="5">
-        <v>13.945</v>
+        <v>12.93</v>
       </c>
       <c r="F30" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D31" s="5">
-        <v>13.9</v>
+        <v>12.775</v>
       </c>
       <c r="E31" s="5">
-        <v>14.06</v>
+        <v>13.435</v>
       </c>
       <c r="F31" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="D32" s="5">
-        <v>13.89</v>
+        <v>12.79</v>
       </c>
       <c r="E32" s="5">
-        <v>13.89</v>
+        <v>13.47</v>
       </c>
       <c r="F32" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="D33" s="5">
-        <v>13.88</v>
+        <v>12.81</v>
       </c>
       <c r="E33" s="5">
-        <v>14.57</v>
+        <v>13.484999999999999</v>
       </c>
       <c r="F33" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="5">
+        <v>12.855</v>
+      </c>
+      <c r="E34" s="5">
+        <v>13.07</v>
+      </c>
+      <c r="F34" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="5">
+        <v>12.914999999999999</v>
+      </c>
+      <c r="E35" s="5">
+        <v>13.414999999999999</v>
+      </c>
+      <c r="F35" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="5">
+        <v>12.93</v>
+      </c>
+      <c r="E36" s="5">
+        <v>13.63</v>
+      </c>
+      <c r="F36" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="5">
-        <v>13.865</v>
-      </c>
-      <c r="E34" s="5">
-        <v>14.44</v>
-      </c>
-      <c r="F34" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D35" s="5">
-        <v>13.865</v>
-      </c>
-      <c r="E35" s="5">
-        <v>13.865</v>
-      </c>
-      <c r="F35" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" s="5">
-        <v>13.845000000000001</v>
-      </c>
-      <c r="E36" s="5">
-        <v>13.845000000000001</v>
-      </c>
-      <c r="F36" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="C37" s="7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D37" s="5">
-        <v>13.73</v>
+        <v>12.98</v>
       </c>
       <c r="E37" s="5">
-        <v>13.73</v>
+        <v>13.71</v>
       </c>
       <c r="F37" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="D38" s="5">
-        <v>13.65</v>
+        <v>12.984999999999999</v>
       </c>
       <c r="E38" s="5">
-        <v>14</v>
+        <v>13.15</v>
       </c>
       <c r="F38" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="D39" s="5">
-        <v>13.63</v>
+        <v>12.984999999999999</v>
       </c>
       <c r="E39" s="5">
-        <v>13.914999999999999</v>
+        <v>13.77</v>
       </c>
       <c r="F39" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="D40" s="5">
-        <v>13.62</v>
+        <v>13.06</v>
       </c>
       <c r="E40" s="5">
-        <v>13.62</v>
+        <v>13.574999999999999</v>
       </c>
       <c r="F40" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="D41" s="5">
-        <v>13.61</v>
+        <v>13.115</v>
       </c>
       <c r="E41" s="5">
-        <v>14.27</v>
+        <v>13.21</v>
       </c>
       <c r="F41" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="D42" s="5">
-        <v>13.605</v>
+        <v>13.17</v>
       </c>
       <c r="E42" s="5">
-        <v>13.855</v>
+        <v>13.74</v>
       </c>
       <c r="F42" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D43" s="5">
-        <v>13.605</v>
+        <v>13.175000000000001</v>
       </c>
       <c r="E43" s="5">
-        <v>13.605</v>
+        <v>13.39</v>
       </c>
       <c r="F43" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D44" s="5">
-        <v>13.56</v>
+        <v>13.244999999999999</v>
       </c>
       <c r="E44" s="5">
-        <v>14.05</v>
+        <v>15.305</v>
       </c>
       <c r="F44" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="D45" s="5">
-        <v>13.494999999999999</v>
+        <v>13.285</v>
       </c>
       <c r="E45" s="5">
         <v>13.62</v>
       </c>
       <c r="F45" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="D46" s="5">
-        <v>13.49</v>
+        <v>13.295</v>
       </c>
       <c r="E46" s="5">
-        <v>14.27</v>
+        <v>13.395</v>
       </c>
       <c r="F46" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="D47" s="5">
-        <v>13.487500000000001</v>
+        <v>13.3</v>
       </c>
       <c r="E47" s="5">
-        <v>13.955</v>
+        <v>13.6</v>
       </c>
       <c r="F47" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="D48" s="5">
-        <v>13.47</v>
+        <v>13.39</v>
       </c>
       <c r="E48" s="5">
-        <v>14.65</v>
+        <v>13.39</v>
       </c>
       <c r="F48" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" s="5">
+        <v>13.4</v>
+      </c>
+      <c r="E49" s="5">
+        <v>13.46</v>
+      </c>
+      <c r="F49" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D50" s="5">
+        <v>13.404999999999999</v>
+      </c>
+      <c r="E50" s="5">
+        <v>13.7</v>
+      </c>
+      <c r="F50" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" s="5">
+        <v>13.41</v>
+      </c>
+      <c r="E51" s="5">
+        <v>13.855</v>
+      </c>
+      <c r="F51" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D49" s="5">
-        <v>13.46</v>
-      </c>
-      <c r="E49" s="5">
-        <v>13.78</v>
-      </c>
-      <c r="F49" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D50" s="5">
-        <v>13.46</v>
-      </c>
-      <c r="E50" s="5">
-        <v>13.984999999999999</v>
-      </c>
-      <c r="F50" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D51" s="5">
-        <v>13.414999999999999</v>
-      </c>
-      <c r="E51" s="5">
-        <v>15.65</v>
-      </c>
-      <c r="F51" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D52" s="5">
         <v>13.41</v>
       </c>
       <c r="E52" s="5">
-        <v>13.855</v>
+        <v>14.38</v>
       </c>
       <c r="F52" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D53" s="5">
+        <v>13.414999999999999</v>
+      </c>
+      <c r="E53" s="5">
+        <v>15.65</v>
+      </c>
+      <c r="F53" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" s="5">
+        <v>13.46</v>
+      </c>
+      <c r="E54" s="5">
+        <v>13.78</v>
+      </c>
+      <c r="F54" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D55" s="5">
+        <v>13.46</v>
+      </c>
+      <c r="E55" s="5">
+        <v>13.984999999999999</v>
+      </c>
+      <c r="F55" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="5">
+        <v>13.47</v>
+      </c>
+      <c r="E56" s="5">
+        <v>14.65</v>
+      </c>
+      <c r="F56" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D53" s="5">
-        <v>13.41</v>
-      </c>
-      <c r="E53" s="5">
-        <v>14.38</v>
-      </c>
-      <c r="F53" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D54" s="5">
-        <v>13.404999999999999</v>
-      </c>
-      <c r="E54" s="5">
-        <v>13.7</v>
-      </c>
-      <c r="F54" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D55" s="5">
-        <v>13.4</v>
-      </c>
-      <c r="E55" s="5">
-        <v>13.46</v>
-      </c>
-      <c r="F55" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D56" s="5">
-        <v>13.39</v>
-      </c>
-      <c r="E56" s="5">
-        <v>13.39</v>
-      </c>
-      <c r="F56" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="D57" s="5">
-        <v>13.3</v>
+        <v>13.487500000000001</v>
       </c>
       <c r="E57" s="5">
-        <v>13.6</v>
+        <v>13.955</v>
       </c>
       <c r="F57" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="D58" s="5">
-        <v>13.295</v>
+        <v>13.49</v>
       </c>
       <c r="E58" s="5">
-        <v>13.395</v>
+        <v>14.27</v>
       </c>
       <c r="F58" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="D59" s="5">
-        <v>13.285</v>
+        <v>13.494999999999999</v>
       </c>
       <c r="E59" s="5">
         <v>13.62</v>
       </c>
       <c r="F59" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D60" s="5">
+        <v>13.56</v>
+      </c>
+      <c r="E60" s="5">
+        <v>14.05</v>
+      </c>
+      <c r="F60" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D61" s="5">
+        <v>13.605</v>
+      </c>
+      <c r="E61" s="5">
+        <v>13.855</v>
+      </c>
+      <c r="F61" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D60" s="5">
-        <v>13.244999999999999</v>
-      </c>
-      <c r="E60" s="5">
-        <v>15.305</v>
-      </c>
-      <c r="F60" s="6">
+    <row r="62" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D62" s="5">
+        <v>13.605</v>
+      </c>
+      <c r="E62" s="5">
+        <v>13.605</v>
+      </c>
+      <c r="F62" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D61" s="5">
-        <v>13.175000000000001</v>
-      </c>
-      <c r="E61" s="5">
-        <v>13.39</v>
-      </c>
-      <c r="F61" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="5">
-        <v>13.17</v>
-      </c>
-      <c r="E62" s="5">
-        <v>13.74</v>
-      </c>
-      <c r="F62" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="C63" s="7" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="D63" s="5">
-        <v>13.115</v>
+        <v>13.61</v>
       </c>
       <c r="E63" s="5">
-        <v>13.21</v>
+        <v>14.27</v>
       </c>
       <c r="F63" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="D64" s="5">
-        <v>13.06</v>
+        <v>13.62</v>
       </c>
       <c r="E64" s="5">
-        <v>13.574999999999999</v>
+        <v>13.62</v>
       </c>
       <c r="F64" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D65" s="5">
-        <v>12.984999999999999</v>
+        <v>13.63</v>
       </c>
       <c r="E65" s="5">
-        <v>13.15</v>
+        <v>13.914999999999999</v>
       </c>
       <c r="F65" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="D66" s="5">
-        <v>12.984999999999999</v>
+        <v>13.65</v>
       </c>
       <c r="E66" s="5">
-        <v>13.77</v>
+        <v>14</v>
       </c>
       <c r="F66" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D67" s="5">
-        <v>12.98</v>
+        <v>13.73</v>
       </c>
       <c r="E67" s="5">
-        <v>13.71</v>
+        <v>13.73</v>
       </c>
       <c r="F67" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D68" s="5">
-        <v>12.93</v>
+        <v>13.845000000000001</v>
       </c>
       <c r="E68" s="5">
-        <v>13.63</v>
+        <v>13.845000000000001</v>
       </c>
       <c r="F68" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="D69" s="5">
-        <v>12.914999999999999</v>
+        <v>13.865</v>
       </c>
       <c r="E69" s="5">
-        <v>13.414999999999999</v>
+        <v>14.44</v>
       </c>
       <c r="F69" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D70" s="5">
-        <v>12.855</v>
+        <v>13.865</v>
       </c>
       <c r="E70" s="5">
-        <v>13.07</v>
+        <v>13.865</v>
       </c>
       <c r="F70" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D71" s="5">
-        <v>12.81</v>
+        <v>13.88</v>
       </c>
       <c r="E71" s="5">
-        <v>13.484999999999999</v>
+        <v>14.57</v>
       </c>
       <c r="F71" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="D72" s="5">
-        <v>12.79</v>
+        <v>13.89</v>
       </c>
       <c r="E72" s="5">
-        <v>13.47</v>
+        <v>13.89</v>
       </c>
       <c r="F72" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D73" s="5">
-        <v>12.775</v>
+        <v>13.9</v>
       </c>
       <c r="E73" s="5">
-        <v>13.435</v>
+        <v>14.06</v>
       </c>
       <c r="F73" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D74" s="5">
+        <v>13.945</v>
+      </c>
+      <c r="E74" s="5">
+        <v>13.945</v>
+      </c>
+      <c r="F74" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D74" s="5">
-        <v>12.74</v>
-      </c>
-      <c r="E74" s="5">
-        <v>13.37</v>
-      </c>
-      <c r="F74" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="B75" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="D75" s="5">
-        <v>12.74</v>
+        <v>13.975</v>
       </c>
       <c r="E75" s="5">
-        <v>12.93</v>
+        <v>14.38</v>
       </c>
       <c r="F75" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D76" s="5">
+        <v>13.994999999999999</v>
+      </c>
+      <c r="E76" s="5">
+        <v>14.4</v>
+      </c>
+      <c r="F76" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D76" s="5">
-        <v>12.72</v>
-      </c>
-      <c r="E76" s="5">
-        <v>14.27</v>
-      </c>
-      <c r="F76" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D77" s="5">
-        <v>12.66</v>
+        <v>14.01</v>
       </c>
       <c r="E77" s="5">
-        <v>13.095000000000001</v>
+        <v>15.32</v>
       </c>
       <c r="F77" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="D78" s="5">
-        <v>12.615</v>
+        <v>14.045</v>
       </c>
       <c r="E78" s="5">
-        <v>13.17</v>
+        <v>15.35</v>
       </c>
       <c r="F78" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D79" s="5">
+        <v>14.06</v>
+      </c>
+      <c r="E79" s="5">
+        <v>14.1</v>
+      </c>
+      <c r="F79" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D80" s="5">
+        <v>14.085000000000001</v>
+      </c>
+      <c r="E80" s="5">
+        <v>14.73</v>
+      </c>
+      <c r="F80" s="6">
         <v>5</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D79" s="5">
-        <v>12.57</v>
-      </c>
-      <c r="E79" s="5">
-        <v>13.52</v>
-      </c>
-      <c r="F79" s="6">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D81" s="5">
+        <v>14.11</v>
+      </c>
+      <c r="E81" s="5">
+        <v>15.08</v>
+      </c>
+      <c r="F81" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B80" s="2" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D82" s="5">
+        <v>14.21</v>
+      </c>
+      <c r="E82" s="5">
+        <v>15.654999999999999</v>
+      </c>
+      <c r="F82" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D83" s="5">
+        <v>14.39</v>
+      </c>
+      <c r="E83" s="5">
+        <v>14.4</v>
+      </c>
+      <c r="F83" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D84" s="5">
+        <v>14.39</v>
+      </c>
+      <c r="E84" s="5">
+        <v>14.39</v>
+      </c>
+      <c r="F84" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D85" s="5">
+        <v>14.52</v>
+      </c>
+      <c r="E85" s="5">
+        <v>15.57</v>
+      </c>
+      <c r="F85" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D86" s="5">
+        <v>14.54</v>
+      </c>
+      <c r="E86" s="5">
+        <v>14.54</v>
+      </c>
+      <c r="F86" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D87" s="5">
+        <v>14.63</v>
+      </c>
+      <c r="E87" s="5">
+        <v>14.8225</v>
+      </c>
+      <c r="F87" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D88" s="5">
+        <v>14.63</v>
+      </c>
+      <c r="E88" s="5">
+        <v>14.63</v>
+      </c>
+      <c r="F88" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C80" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D80" s="5">
-        <v>12.57</v>
-      </c>
-      <c r="E80" s="5">
-        <v>12.57</v>
-      </c>
-      <c r="F80" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D81" s="5">
-        <v>12.55</v>
-      </c>
-      <c r="E81" s="5">
-        <v>13.68</v>
-      </c>
-      <c r="F81" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+      <c r="C89" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D89" s="5">
+        <v>14.63</v>
+      </c>
+      <c r="E89" s="5">
+        <v>14.63</v>
+      </c>
+      <c r="F89" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D82" s="5">
-        <v>12.54</v>
-      </c>
-      <c r="E82" s="5">
-        <v>13.05</v>
-      </c>
-      <c r="F82" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D83" s="5">
-        <v>12.525</v>
-      </c>
-      <c r="E83" s="5">
-        <v>12.525</v>
-      </c>
-      <c r="F83" s="6">
+      <c r="B90" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D90" s="5">
+        <v>14.78</v>
+      </c>
+      <c r="E90" s="5">
+        <v>14.78</v>
+      </c>
+      <c r="F90" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D84" s="5">
-        <v>12.52</v>
-      </c>
-      <c r="E84" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="F84" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D85" s="5">
-        <v>12.484999999999999</v>
-      </c>
-      <c r="E85" s="5">
-        <v>12.484999999999999</v>
-      </c>
-      <c r="F85" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D86" s="5">
-        <v>12.48</v>
-      </c>
-      <c r="E86" s="5">
-        <v>15.08</v>
-      </c>
-      <c r="F86" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D87" s="5">
-        <v>12.45</v>
-      </c>
-      <c r="E87" s="5">
-        <v>14.32</v>
-      </c>
-      <c r="F87" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D88" s="5">
-        <v>12.44</v>
-      </c>
-      <c r="E88" s="5">
-        <v>13.43</v>
-      </c>
-      <c r="F88" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D89" s="5">
-        <v>12.42</v>
-      </c>
-      <c r="E89" s="5">
-        <v>13.33</v>
-      </c>
-      <c r="F89" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D90" s="5">
-        <v>12.395</v>
-      </c>
-      <c r="E90" s="5">
-        <v>12.82</v>
-      </c>
-      <c r="F90" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D91" s="5">
-        <v>12.37</v>
+        <v>14.785</v>
       </c>
       <c r="E91" s="5">
-        <v>12.37</v>
+        <v>15.15</v>
       </c>
       <c r="F91" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D92" s="5">
+        <v>14.85</v>
+      </c>
+      <c r="E92" s="5">
+        <v>14.9</v>
+      </c>
+      <c r="F92" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D93" s="5">
+        <v>14.9</v>
+      </c>
+      <c r="E93" s="5">
+        <v>14.9</v>
+      </c>
+      <c r="F93" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D92" s="5">
-        <v>12.34</v>
-      </c>
-      <c r="E92" s="5">
-        <v>12.34</v>
-      </c>
-      <c r="F92" s="6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D94" s="5">
+        <v>15.005000000000001</v>
+      </c>
+      <c r="E94" s="5">
+        <v>15.005000000000001</v>
+      </c>
+      <c r="F94" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D93" s="5">
-        <v>12.32</v>
-      </c>
-      <c r="E93" s="5">
-        <v>12.33</v>
-      </c>
-      <c r="F93" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D94" s="5">
-        <v>12.265000000000001</v>
-      </c>
-      <c r="E94" s="5">
-        <v>13.12</v>
-      </c>
-      <c r="F94" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="D95" s="5">
-        <v>12.25</v>
+        <v>15.02</v>
       </c>
       <c r="E95" s="5">
-        <v>12.36</v>
+        <v>15.02</v>
       </c>
       <c r="F95" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="D96" s="5">
-        <v>12.135</v>
+        <v>15.04</v>
       </c>
       <c r="E96" s="5">
-        <v>12.35</v>
+        <v>15.04</v>
       </c>
       <c r="F96" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="D97" s="5">
-        <v>12.035</v>
+        <v>15.05</v>
       </c>
       <c r="E97" s="5">
-        <v>12.08</v>
+        <v>15.545</v>
       </c>
       <c r="F97" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D98" s="5">
+        <v>15.21</v>
+      </c>
+      <c r="E98" s="5">
+        <v>16.872499999999999</v>
+      </c>
+      <c r="F98" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D99" s="5">
+        <v>15.44</v>
+      </c>
+      <c r="E99" s="5">
+        <v>15.44</v>
+      </c>
+      <c r="F99" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B100" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C98" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D98" s="5">
-        <v>11.96</v>
-      </c>
-      <c r="E98" s="5">
-        <v>12.76</v>
-      </c>
-      <c r="F98" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D99" s="5">
-        <v>11.855</v>
-      </c>
-      <c r="E99" s="5">
-        <v>13.13</v>
-      </c>
-      <c r="F99" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="C100" s="7" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="D100" s="5">
-        <v>11.85</v>
+        <v>15.51</v>
       </c>
       <c r="E100" s="5">
-        <v>12.574999999999999</v>
+        <v>15.51</v>
       </c>
       <c r="F100" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="B101" s="2" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="D101" s="5">
-        <v>11.425000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="E101" s="5">
-        <v>11.425000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="F101" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D102" s="5">
-        <v>11.27</v>
+        <v>15.67</v>
       </c>
       <c r="E102" s="5">
-        <v>12.86</v>
+        <v>16.6175</v>
       </c>
       <c r="F102" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>5</v>
       </c>
@@ -4984,7 +5038,7 @@
       <c r="E103" s="5"/>
       <c r="F103" s="6"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>5</v>
       </c>
@@ -4998,7 +5052,7 @@
       <c r="E104" s="5"/>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>5</v>
       </c>
@@ -5012,7 +5066,7 @@
       <c r="E105" s="5"/>
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>5</v>
       </c>
@@ -5022,11 +5076,11 @@
       <c r="C106" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D106" s="16"/>
-      <c r="E106" s="16"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="15"/>
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>5</v>
       </c>
@@ -5036,11 +5090,11 @@
       <c r="C107" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D107" s="16"/>
-      <c r="E107" s="16"/>
+      <c r="D107" s="15"/>
+      <c r="E107" s="15"/>
       <c r="F107" s="6"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>12</v>
       </c>
@@ -5054,7 +5108,7 @@
       <c r="E108" s="5"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>12</v>
       </c>
@@ -5068,7 +5122,7 @@
       <c r="E109" s="5"/>
       <c r="F109" s="6"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>12</v>
       </c>
@@ -5082,7 +5136,7 @@
       <c r="E110" s="5"/>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>12</v>
       </c>
@@ -5096,7 +5150,7 @@
       <c r="E111" s="5"/>
       <c r="F111" s="6"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>12</v>
       </c>
@@ -5110,7 +5164,7 @@
       <c r="E112" s="5"/>
       <c r="F112" s="6"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>24</v>
       </c>
@@ -5124,7 +5178,7 @@
       <c r="E113" s="5"/>
       <c r="F113" s="6"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>24</v>
       </c>
@@ -5138,7 +5192,7 @@
       <c r="E114" s="5"/>
       <c r="F114" s="6"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>24</v>
       </c>
@@ -5152,7 +5206,7 @@
       <c r="E115" s="5"/>
       <c r="F115" s="6"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>24</v>
       </c>
@@ -5166,7 +5220,7 @@
       <c r="E116" s="5"/>
       <c r="F116" s="6"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>24</v>
       </c>
@@ -5180,7 +5234,7 @@
       <c r="E117" s="5"/>
       <c r="F117" s="6"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>24</v>
       </c>
@@ -5194,7 +5248,7 @@
       <c r="E118" s="5"/>
       <c r="F118" s="6"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>24</v>
       </c>
@@ -5208,7 +5262,7 @@
       <c r="E119" s="5"/>
       <c r="F119" s="6"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>24</v>
       </c>
@@ -5222,7 +5276,7 @@
       <c r="E120" s="5"/>
       <c r="F120" s="6"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>24</v>
       </c>
@@ -5236,7 +5290,7 @@
       <c r="E121" s="5"/>
       <c r="F121" s="6"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>24</v>
       </c>
@@ -5250,7 +5304,7 @@
       <c r="E122" s="5"/>
       <c r="F122" s="6"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>24</v>
       </c>
@@ -5264,7 +5318,7 @@
       <c r="E123" s="5"/>
       <c r="F123" s="6"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
         <v>24</v>
       </c>
@@ -5276,13 +5330,13 @@
       </c>
       <c r="F124" s="6"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F125" s="19"/>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F125" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F124" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F124">
-      <sortCondition descending="1" ref="D1:D106"/>
+      <sortCondition ref="D1:D124"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5292,7 +5346,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -5301,7 +5355,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5321,7 +5375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -5349,17 +5403,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="76" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="95.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5379,7 +5434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -5399,7 +5454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -5419,7 +5474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -5438,8 +5493,11 @@
       <c r="F4" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -5458,8 +5516,11 @@
       <c r="F5" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -5479,7 +5540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="145" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -5492,8 +5553,11 @@
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="17" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="205.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -5512,8 +5576,11 @@
       <c r="F8" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G8" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -5526,8 +5593,11 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" s="17" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -5546,8 +5616,11 @@
       <c r="F10" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="17" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
@@ -5567,7 +5640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -5581,7 +5654,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -5601,7 +5674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -5621,7 +5694,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -5641,7 +5714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
@@ -5661,7 +5734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
@@ -5681,7 +5754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -5701,7 +5774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
@@ -5721,7 +5794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
@@ -5741,7 +5814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>5</v>
       </c>
@@ -5761,7 +5834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
@@ -5772,7 +5845,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>5</v>
       </c>
@@ -5792,7 +5865,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -5801,7 +5874,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5821,7 +5894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -5841,7 +5914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -5861,7 +5934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -5881,21 +5954,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="5">
+        <v>13.41</v>
+      </c>
+      <c r="E5" s="5">
+        <v>13.855</v>
+      </c>
+      <c r="F5" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -5915,27 +5994,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="5">
-        <v>13.41</v>
-      </c>
-      <c r="E7" s="5">
-        <v>13.855</v>
-      </c>
-      <c r="F7" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -5955,7 +6028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -5975,7 +6048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -5983,61 +6056,79 @@
         <v>16</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D10" s="5">
-        <v>12.42</v>
+        <v>12.37</v>
       </c>
       <c r="E10" s="5">
-        <v>13.33</v>
+        <v>12.37</v>
       </c>
       <c r="F10" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="5">
+        <v>12.42</v>
+      </c>
+      <c r="E11" s="5">
+        <v>13.33</v>
+      </c>
+      <c r="F11" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C12" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="5">
+        <v>12.48</v>
+      </c>
+      <c r="E12" s="5">
+        <v>15.08</v>
+      </c>
+      <c r="F12" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="5">
+        <v>12.54</v>
+      </c>
+      <c r="E13" s="5">
+        <v>13.05</v>
+      </c>
+      <c r="F13" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -6045,19 +6136,19 @@
         <v>16</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D14" s="5">
-        <v>12.48</v>
+        <v>12.74</v>
       </c>
       <c r="E14" s="5">
-        <v>15.08</v>
+        <v>13.37</v>
       </c>
       <c r="F14" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -6065,19 +6156,19 @@
         <v>16</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" s="5">
-        <v>12.81</v>
+        <v>12.775</v>
       </c>
       <c r="E15" s="5">
-        <v>13.484999999999999</v>
+        <v>13.435</v>
       </c>
       <c r="F15" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
@@ -6085,79 +6176,61 @@
         <v>16</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16" s="5">
-        <v>12.775</v>
+        <v>12.81</v>
       </c>
       <c r="E16" s="5">
-        <v>13.435</v>
+        <v>13.484999999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="5">
-        <v>12.74</v>
-      </c>
-      <c r="E17" s="5">
-        <v>13.37</v>
-      </c>
-      <c r="F17" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="5">
-        <v>12.54</v>
-      </c>
-      <c r="E18" s="5">
-        <v>13.05</v>
-      </c>
-      <c r="F18" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C18" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="5">
-        <v>12.37</v>
-      </c>
-      <c r="E19" s="5">
-        <v>12.37</v>
-      </c>
-      <c r="F19" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C19" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
@@ -6165,19 +6238,19 @@
         <v>17</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D20" s="5">
-        <v>14.785</v>
+        <v>13.494999999999999</v>
       </c>
       <c r="E20" s="5">
-        <v>15.15</v>
+        <v>13.62</v>
       </c>
       <c r="F20" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -6197,7 +6270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>12</v>
       </c>
@@ -6217,41 +6290,41 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="5">
+        <v>14.785</v>
+      </c>
+      <c r="E23" s="5">
+        <v>15.15</v>
+      </c>
+      <c r="F23" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="5">
-        <v>13.494999999999999</v>
-      </c>
-      <c r="E24" s="5">
-        <v>13.62</v>
-      </c>
-      <c r="F24" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C24" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -6259,19 +6332,19 @@
         <v>18</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D25" s="5">
-        <v>15.005000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="E25" s="5">
-        <v>15.005000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="F25" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
@@ -6279,19 +6352,19 @@
         <v>18</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D26" s="5">
-        <v>15.44</v>
+        <v>14.78</v>
       </c>
       <c r="E26" s="5">
-        <v>15.44</v>
+        <v>14.78</v>
       </c>
       <c r="F26" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>12</v>
       </c>
@@ -6311,7 +6384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>12</v>
       </c>
@@ -6319,19 +6392,19 @@
         <v>18</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D28" s="5">
-        <v>14.78</v>
+        <v>15.005000000000001</v>
       </c>
       <c r="E28" s="5">
-        <v>14.78</v>
+        <v>15.005000000000001</v>
       </c>
       <c r="F28" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -6339,19 +6412,19 @@
         <v>18</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D29" s="5">
-        <v>13.3</v>
+        <v>15.44</v>
       </c>
       <c r="E29" s="5">
-        <v>13.6</v>
+        <v>15.44</v>
       </c>
       <c r="F29" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>12</v>
       </c>
@@ -6371,7 +6444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
@@ -6379,19 +6452,19 @@
         <v>20</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D31" s="5">
-        <v>13.4</v>
+        <v>13.39</v>
       </c>
       <c r="E31" s="5">
-        <v>13.46</v>
+        <v>13.39</v>
       </c>
       <c r="F31" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
@@ -6399,19 +6472,19 @@
         <v>20</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D32" s="5">
-        <v>13.39</v>
+        <v>13.4</v>
       </c>
       <c r="E32" s="5">
-        <v>13.39</v>
+        <v>13.46</v>
       </c>
       <c r="F32" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -6419,19 +6492,19 @@
         <v>20</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D33" s="5">
-        <v>13.975</v>
+        <v>13.605</v>
       </c>
       <c r="E33" s="5">
-        <v>14.38</v>
+        <v>13.855</v>
       </c>
       <c r="F33" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>12</v>
       </c>
@@ -6439,19 +6512,19 @@
         <v>20</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D34" s="5">
-        <v>13.605</v>
+        <v>13.975</v>
       </c>
       <c r="E34" s="5">
-        <v>13.855</v>
+        <v>14.38</v>
       </c>
       <c r="F34" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
@@ -6471,7 +6544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
@@ -6491,7 +6564,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>12</v>
       </c>
@@ -6512,7 +6585,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F37" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:F37" xr:uid="{00000000-0009-0000-0000-000004000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F37">
+      <sortCondition ref="B1:B37"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6520,7 +6597,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -6529,7 +6606,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6549,7 +6626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -6578,7 +6655,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -6587,7 +6664,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6607,7 +6684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -6627,7 +6704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -6641,7 +6718,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -6661,7 +6738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -6675,7 +6752,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -6695,7 +6772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -6715,7 +6792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -6735,7 +6812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -6755,7 +6832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -6775,7 +6852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -6795,7 +6872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -6815,7 +6892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -6835,7 +6912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -6855,7 +6932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -6875,7 +6952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -6895,7 +6972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -6915,7 +6992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -6929,7 +7006,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
@@ -6943,7 +7020,7 @@
       <c r="E19" s="5"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
@@ -6957,7 +7034,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
@@ -6977,7 +7054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
@@ -6997,7 +7074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
@@ -7017,7 +7094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
@@ -7037,7 +7114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -7057,7 +7134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
@@ -7077,7 +7154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>24</v>
       </c>
@@ -7097,7 +7174,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
@@ -7117,7 +7194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
@@ -7137,7 +7214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
@@ -7157,7 +7234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>24</v>
       </c>
@@ -7177,7 +7254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>24</v>
       </c>
@@ -7191,7 +7268,7 @@
       <c r="E32" s="5"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>24</v>
       </c>
@@ -7211,7 +7288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>24</v>
       </c>
@@ -7225,7 +7302,7 @@
       <c r="E34" s="5"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>24</v>
       </c>
@@ -7239,7 +7316,7 @@
       <c r="E35" s="5"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>24</v>
       </c>
@@ -7259,7 +7336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>24</v>
       </c>
@@ -7279,7 +7356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>24</v>
       </c>
@@ -7299,7 +7376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>24</v>
       </c>
@@ -7319,7 +7396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>24</v>
       </c>
@@ -7339,7 +7416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>24</v>
       </c>
@@ -7359,7 +7436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>24</v>
       </c>
@@ -7379,7 +7456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>24</v>
       </c>
@@ -7399,7 +7476,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>24</v>
       </c>
@@ -7419,7 +7496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>24</v>
       </c>
@@ -7433,7 +7510,7 @@
       <c r="E45" s="5"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>24</v>
       </c>
@@ -7447,7 +7524,7 @@
       <c r="E46" s="5"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>24</v>
       </c>
@@ -7467,7 +7544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>24</v>
       </c>
@@ -7487,7 +7564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>24</v>
       </c>
@@ -7507,7 +7584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>24</v>
       </c>
@@ -7527,7 +7604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>24</v>
       </c>
@@ -7547,7 +7624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>24</v>
       </c>
@@ -7567,7 +7644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>24</v>
       </c>
@@ -7587,7 +7664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>24</v>
       </c>
@@ -7601,7 +7678,7 @@
       <c r="E54" s="5"/>
       <c r="F54" s="6"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>24</v>
       </c>
@@ -7621,7 +7698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>24</v>
       </c>
@@ -7641,7 +7718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>24</v>
       </c>
@@ -7661,7 +7738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>24</v>
       </c>
@@ -7681,7 +7758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>24</v>
       </c>
@@ -7701,7 +7778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>24</v>
       </c>
@@ -7721,7 +7798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>24</v>
       </c>
@@ -7741,7 +7818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>24</v>
       </c>
@@ -7761,7 +7838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>24</v>
       </c>
@@ -7781,7 +7858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>24</v>
       </c>
@@ -7801,7 +7878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>24</v>
       </c>
@@ -7821,7 +7898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>24</v>
       </c>
@@ -7841,7 +7918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>24</v>
       </c>
@@ -7861,7 +7938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>24</v>
       </c>
@@ -7881,7 +7958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>24</v>
       </c>
@@ -7901,7 +7978,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
         <v>24</v>
       </c>
